--- a/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
+++ b/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -400,10 +400,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2">
-        <v>46269</v>
+        <v>46278</v>
       </c>
       <c r="B2">
-        <v>8.952</v>
+        <v>13.828</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -411,10 +411,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2">
-        <v>46269.01041666666</v>
+        <v>46278.01041666666</v>
       </c>
       <c r="B3">
-        <v>14.387</v>
+        <v>7.611</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -422,164 +422,164 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2">
-        <v>46269.02083333334</v>
+        <v>46278.02083333334</v>
       </c>
       <c r="B4">
-        <v>3.347</v>
+        <v>7.591</v>
       </c>
       <c r="C4">
-        <v>0.477</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2">
-        <v>46269.03125</v>
+        <v>46278.03125</v>
       </c>
       <c r="B5">
-        <v>7.707</v>
+        <v>2.12</v>
       </c>
       <c r="C5">
-        <v>0.013</v>
+        <v>0.217</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2">
-        <v>46269.04166666666</v>
+        <v>46278.04166666666</v>
       </c>
       <c r="B6">
-        <v>3.574</v>
+        <v>1.573</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>1.818</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2">
-        <v>46269.05208333334</v>
+        <v>46278.05208333334</v>
       </c>
       <c r="B7">
-        <v>4.092</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>1.683</v>
+        <v>5.981</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2">
-        <v>46269.0625</v>
+        <v>46278.0625</v>
       </c>
       <c r="B8">
-        <v>3.571</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>0.327</v>
+        <v>39.871</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2">
-        <v>46269.07291666666</v>
+        <v>46278.07291666666</v>
       </c>
       <c r="B9">
-        <v>0.914</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="C9">
-        <v>2.145</v>
+        <v>22.838</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2">
-        <v>46269.08333333334</v>
+        <v>46278.08333333334</v>
       </c>
       <c r="B10">
-        <v>0.768</v>
+        <v>0.079</v>
       </c>
       <c r="C10">
-        <v>0.856</v>
+        <v>9.632</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2">
-        <v>46269.09375</v>
+        <v>46278.09375</v>
       </c>
       <c r="B11">
-        <v>5.084</v>
+        <v>0.101</v>
       </c>
       <c r="C11">
-        <v>0.167</v>
+        <v>8.622</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2">
-        <v>46269.10416666666</v>
+        <v>46278.10416666666</v>
       </c>
       <c r="B12">
-        <v>0.63</v>
+        <v>0.137</v>
       </c>
       <c r="C12">
-        <v>4.397</v>
+        <v>5.076</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2">
-        <v>46269.11458333334</v>
+        <v>46278.11458333334</v>
       </c>
       <c r="B13">
-        <v>0.782</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="C13">
-        <v>1.76</v>
+        <v>8.318</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2">
-        <v>46269.125</v>
+        <v>46278.125</v>
       </c>
       <c r="B14">
-        <v>9.9</v>
+        <v>3.639</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>1.096</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2">
-        <v>46269.13541666666</v>
+        <v>46278.13541666666</v>
       </c>
       <c r="B15">
-        <v>11.49</v>
+        <v>1.314</v>
       </c>
       <c r="C15">
-        <v>0.079</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2">
-        <v>46269.14583333334</v>
+        <v>46278.14583333334</v>
       </c>
       <c r="B16">
-        <v>3.687</v>
+        <v>3.425</v>
       </c>
       <c r="C16">
-        <v>2.247</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2">
-        <v>46269.15625</v>
+        <v>46278.15625</v>
       </c>
       <c r="B17">
-        <v>2.135</v>
+        <v>8.065</v>
       </c>
       <c r="C17">
-        <v>0.627</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2">
-        <v>46269.16666666666</v>
+        <v>46278.16666666666</v>
       </c>
       <c r="B18">
-        <v>8.403</v>
+        <v>2.307</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -587,10 +587,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2">
-        <v>46269.17708333334</v>
+        <v>46278.17708333334</v>
       </c>
       <c r="B19">
-        <v>4.773</v>
+        <v>3.592</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -598,32 +598,32 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2">
-        <v>46269.1875</v>
+        <v>46278.1875</v>
       </c>
       <c r="B20">
-        <v>0.229</v>
+        <v>2.63</v>
       </c>
       <c r="C20">
-        <v>5.547</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2">
-        <v>46269.19791666666</v>
+        <v>46278.19791666666</v>
       </c>
       <c r="B21">
-        <v>0.947</v>
+        <v>5.47</v>
       </c>
       <c r="C21">
-        <v>3.407</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2">
-        <v>46269.20833333334</v>
+        <v>46278.20833333334</v>
       </c>
       <c r="B22">
-        <v>1.678</v>
+        <v>11.42</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -631,298 +631,177 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2">
-        <v>46269.21875</v>
+        <v>46278.21875</v>
       </c>
       <c r="B23">
-        <v>1.841</v>
+        <v>1.013</v>
       </c>
       <c r="C23">
-        <v>0.206</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2">
-        <v>46269.22916666666</v>
+        <v>46278.22916666666</v>
       </c>
       <c r="B24">
-        <v>1.465</v>
+        <v>1.346</v>
       </c>
       <c r="C24">
-        <v>0.674</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2">
-        <v>46269.23958333334</v>
+        <v>46278.23958333334</v>
       </c>
       <c r="B25">
-        <v>3.735</v>
+        <v>2.157</v>
       </c>
       <c r="C25">
-        <v>0.004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2">
-        <v>46269.25</v>
+        <v>46278.25</v>
       </c>
       <c r="B26">
-        <v>0.218</v>
+        <v>0.042</v>
       </c>
       <c r="C26">
-        <v>5.117</v>
+        <v>13.216</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2">
-        <v>46269.26041666666</v>
+        <v>46278.26041666666</v>
       </c>
       <c r="B27">
-        <v>1.597</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>3.013</v>
+        <v>30.463</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2">
-        <v>46269.27083333334</v>
+        <v>46278.27083333334</v>
       </c>
       <c r="B28">
-        <v>3.756</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>3.075</v>
+        <v>26.463</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2">
-        <v>46269.28125</v>
+        <v>46278.28125</v>
       </c>
       <c r="B29">
-        <v>10.575</v>
+        <v>0</v>
       </c>
       <c r="C29">
-        <v>2.613</v>
+        <v>41.877</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2">
-        <v>46269.29166666666</v>
+        <v>46278.29166666666</v>
       </c>
       <c r="B30">
-        <v>1.501</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="C30">
-        <v>15.87</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2">
-        <v>46269.30208333334</v>
+        <v>46278.30208333334</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="C31">
-        <v>10.941</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2">
-        <v>46269.3125</v>
+        <v>46278.3125</v>
       </c>
       <c r="B32">
         <v>0</v>
       </c>
       <c r="C32">
-        <v>12.667</v>
+        <v>20.296</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2">
-        <v>46269.32291666666</v>
+        <v>46278.32291666666</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>0.051</v>
       </c>
       <c r="C33">
-        <v>53.807</v>
+        <v>4.306</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2">
-        <v>46269.33333333334</v>
+        <v>46278.33333333334</v>
       </c>
       <c r="B34">
         <v>0</v>
       </c>
       <c r="C34">
-        <v>81.405</v>
+        <v>13.101</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2">
-        <v>46269.34375</v>
+        <v>46278.34375</v>
       </c>
       <c r="B35">
         <v>0</v>
       </c>
       <c r="C35">
-        <v>38.285</v>
+        <v>18.188</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2">
-        <v>46269.35416666666</v>
+        <v>46278.35416666666</v>
       </c>
       <c r="B36">
-        <v>4.808</v>
+        <v>0.097</v>
       </c>
       <c r="C36">
-        <v>1.779</v>
+        <v>16.694</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2">
-        <v>46269.36458333334</v>
+        <v>46278.36458333334</v>
       </c>
       <c r="B37">
-        <v>0.383</v>
+        <v>0</v>
       </c>
       <c r="C37">
-        <v>4.058</v>
+        <v>24.661</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2">
-        <v>46269.375</v>
+        <v>46278.375</v>
       </c>
       <c r="B38">
-        <v>33.466</v>
+        <v>0</v>
       </c>
       <c r="C38">
-        <v>0.028</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="2">
-        <v>46269.38541666666</v>
-      </c>
-      <c r="B39">
-        <v>2.227</v>
-      </c>
-      <c r="C39">
-        <v>0.149</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="2">
-        <v>46269.39583333334</v>
-      </c>
-      <c r="B40">
-        <v>0.237</v>
-      </c>
-      <c r="C40">
-        <v>13.624</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="2">
-        <v>46269.40625</v>
-      </c>
-      <c r="B41">
-        <v>0</v>
-      </c>
-      <c r="C41">
-        <v>29.993</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="2">
-        <v>46269.41666666666</v>
-      </c>
-      <c r="B42">
-        <v>0</v>
-      </c>
-      <c r="C42">
-        <v>40.437</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="2">
-        <v>46269.42708333334</v>
-      </c>
-      <c r="B43">
-        <v>0</v>
-      </c>
-      <c r="C43">
-        <v>25.414</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="2">
-        <v>46269.4375</v>
-      </c>
-      <c r="B44">
-        <v>0</v>
-      </c>
-      <c r="C44">
-        <v>23.658</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="2">
-        <v>46269.44791666666</v>
-      </c>
-      <c r="B45">
-        <v>0</v>
-      </c>
-      <c r="C45">
-        <v>17.522</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="2">
-        <v>46269.45833333334</v>
-      </c>
-      <c r="B46">
-        <v>0</v>
-      </c>
-      <c r="C46">
-        <v>11.186</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="2">
-        <v>46269.46875</v>
-      </c>
-      <c r="B47">
-        <v>0</v>
-      </c>
-      <c r="C47">
-        <v>9.417999999999999</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="2">
-        <v>46269.47916666666</v>
-      </c>
-      <c r="B48">
-        <v>0</v>
-      </c>
-      <c r="C48">
-        <v>6.034</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="2">
-        <v>46269.48958333334</v>
-      </c>
-      <c r="B49">
-        <v>0</v>
-      </c>
-      <c r="C49">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
+++ b/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -400,153 +400,153 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2">
-        <v>46278</v>
+        <v>46283</v>
       </c>
       <c r="B2">
-        <v>13.828</v>
+        <v>0.242</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>11.108</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2">
-        <v>46278.01041666666</v>
+        <v>46283.01041666666</v>
       </c>
       <c r="B3">
-        <v>7.611</v>
+        <v>0.063</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>2.476</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2">
-        <v>46278.02083333334</v>
+        <v>46283.02083333334</v>
       </c>
       <c r="B4">
-        <v>7.591</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>0.025</v>
+        <v>11.817</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2">
-        <v>46278.03125</v>
+        <v>46283.03125</v>
       </c>
       <c r="B5">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>0.217</v>
+        <v>12.029</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2">
-        <v>46278.04166666666</v>
+        <v>46283.04166666666</v>
       </c>
       <c r="B6">
-        <v>1.573</v>
+        <v>2.32</v>
       </c>
       <c r="C6">
-        <v>1.818</v>
+        <v>2.637</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2">
-        <v>46278.05208333334</v>
+        <v>46283.05208333334</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>0.144</v>
       </c>
       <c r="C7">
-        <v>5.981</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2">
-        <v>46278.0625</v>
+        <v>46283.0625</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>2.646</v>
       </c>
       <c r="C8">
-        <v>39.871</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2">
-        <v>46278.07291666666</v>
+        <v>46283.07291666666</v>
       </c>
       <c r="B9">
-        <v>0.008999999999999999</v>
+        <v>3.476</v>
       </c>
       <c r="C9">
-        <v>22.838</v>
+        <v>0.5669999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2">
-        <v>46278.08333333334</v>
+        <v>46283.08333333334</v>
       </c>
       <c r="B10">
-        <v>0.079</v>
+        <v>0.001</v>
       </c>
       <c r="C10">
-        <v>9.632</v>
+        <v>7.879</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2">
-        <v>46278.09375</v>
+        <v>46283.09375</v>
       </c>
       <c r="B11">
-        <v>0.101</v>
+        <v>2.593</v>
       </c>
       <c r="C11">
-        <v>8.622</v>
+        <v>0.787</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2">
-        <v>46278.10416666666</v>
+        <v>46283.10416666666</v>
       </c>
       <c r="B12">
-        <v>0.137</v>
+        <v>0.379</v>
       </c>
       <c r="C12">
-        <v>5.076</v>
+        <v>2.317</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2">
-        <v>46278.11458333334</v>
+        <v>46283.11458333334</v>
       </c>
       <c r="B13">
-        <v>0.06900000000000001</v>
+        <v>1.643</v>
       </c>
       <c r="C13">
-        <v>8.318</v>
+        <v>1.091</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2">
-        <v>46278.125</v>
+        <v>46283.125</v>
       </c>
       <c r="B14">
-        <v>3.639</v>
+        <v>0.477</v>
       </c>
       <c r="C14">
-        <v>1.096</v>
+        <v>2.528</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2">
-        <v>46278.13541666666</v>
+        <v>46283.13541666666</v>
       </c>
       <c r="B15">
-        <v>1.314</v>
+        <v>2.251</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -554,10 +554,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2">
-        <v>46278.14583333334</v>
+        <v>46283.14583333334</v>
       </c>
       <c r="B16">
-        <v>3.425</v>
+        <v>2.045</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -565,32 +565,32 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2">
-        <v>46278.15625</v>
+        <v>46283.15625</v>
       </c>
       <c r="B17">
-        <v>8.065</v>
+        <v>3.519</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>0.134</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2">
-        <v>46278.16666666666</v>
+        <v>46283.16666666666</v>
       </c>
       <c r="B18">
-        <v>2.307</v>
+        <v>1.82</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>1.731</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2">
-        <v>46278.17708333334</v>
+        <v>46283.17708333334</v>
       </c>
       <c r="B19">
-        <v>3.592</v>
+        <v>1.685</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -598,10 +598,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2">
-        <v>46278.1875</v>
+        <v>46283.1875</v>
       </c>
       <c r="B20">
-        <v>2.63</v>
+        <v>1.778</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -609,10 +609,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2">
-        <v>46278.19791666666</v>
+        <v>46283.19791666666</v>
       </c>
       <c r="B21">
-        <v>5.47</v>
+        <v>3.58</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -620,10 +620,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2">
-        <v>46278.20833333334</v>
+        <v>46283.20833333334</v>
       </c>
       <c r="B22">
-        <v>11.42</v>
+        <v>22.262</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -631,10 +631,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2">
-        <v>46278.21875</v>
+        <v>46283.21875</v>
       </c>
       <c r="B23">
-        <v>1.013</v>
+        <v>6.94</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -642,10 +642,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2">
-        <v>46278.22916666666</v>
+        <v>46283.22916666666</v>
       </c>
       <c r="B24">
-        <v>1.346</v>
+        <v>1.551</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -653,10 +653,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2">
-        <v>46278.23958333334</v>
+        <v>46283.23958333334</v>
       </c>
       <c r="B25">
-        <v>2.157</v>
+        <v>2.711</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -664,144 +664,210 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2">
-        <v>46278.25</v>
+        <v>46283.25</v>
       </c>
       <c r="B26">
-        <v>0.042</v>
+        <v>1.112</v>
       </c>
       <c r="C26">
-        <v>13.216</v>
+        <v>0.988</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2">
-        <v>46278.26041666666</v>
+        <v>46283.26041666666</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="C27">
-        <v>30.463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2">
-        <v>46278.27083333334</v>
+        <v>46283.27083333334</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>1.966</v>
       </c>
       <c r="C28">
-        <v>26.463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2">
-        <v>46278.28125</v>
+        <v>46283.28125</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>0.183</v>
       </c>
       <c r="C29">
-        <v>41.877</v>
+        <v>1.059</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2">
-        <v>46278.29166666666</v>
+        <v>46283.29166666666</v>
       </c>
       <c r="B30">
-        <v>0.6850000000000001</v>
+        <v>6.221</v>
       </c>
       <c r="C30">
-        <v>2.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2">
-        <v>46278.30208333334</v>
+        <v>46283.30208333334</v>
       </c>
       <c r="B31">
-        <v>0.008</v>
+        <v>10.405</v>
       </c>
       <c r="C31">
-        <v>5.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2">
-        <v>46278.3125</v>
+        <v>46283.3125</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>13.982</v>
       </c>
       <c r="C32">
-        <v>20.296</v>
+        <v>1.869</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2">
-        <v>46278.32291666666</v>
+        <v>46283.32291666666</v>
       </c>
       <c r="B33">
-        <v>0.051</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <v>4.306</v>
+        <v>37.76</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2">
-        <v>46278.33333333334</v>
+        <v>46283.33333333334</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>0.239</v>
       </c>
       <c r="C34">
-        <v>13.101</v>
+        <v>40.008</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2">
-        <v>46278.34375</v>
+        <v>46283.34375</v>
       </c>
       <c r="B35">
         <v>0</v>
       </c>
       <c r="C35">
-        <v>18.188</v>
+        <v>62.967</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2">
-        <v>46278.35416666666</v>
+        <v>46283.35416666666</v>
       </c>
       <c r="B36">
-        <v>0.097</v>
+        <v>1.444</v>
       </c>
       <c r="C36">
-        <v>16.694</v>
+        <v>10.193</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2">
-        <v>46278.36458333334</v>
+        <v>46283.36458333334</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>8.275</v>
       </c>
       <c r="C37">
-        <v>24.661</v>
+        <v>0.096</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2">
-        <v>46278.375</v>
+        <v>46283.375</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>7.263</v>
       </c>
       <c r="C38">
+        <v>0.144</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="2">
+        <v>46283.38541666666</v>
+      </c>
+      <c r="B39">
+        <v>5.639</v>
+      </c>
+      <c r="C39">
+        <v>0.678</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="2">
+        <v>46283.39583333334</v>
+      </c>
+      <c r="B40">
+        <v>16.465</v>
+      </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="2">
+        <v>46283.40625</v>
+      </c>
+      <c r="B41">
+        <v>14.093</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="2">
+        <v>46283.41666666666</v>
+      </c>
+      <c r="B42">
+        <v>53.474</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="2">
+        <v>46283.42708333334</v>
+      </c>
+      <c r="B43">
+        <v>29.836</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="2">
+        <v>46283.4375</v>
+      </c>
+      <c r="B44">
+        <v>0</v>
+      </c>
+      <c r="C44">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
+++ b/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -400,76 +400,76 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2">
-        <v>46283</v>
+        <v>46285</v>
       </c>
       <c r="B2">
-        <v>0.242</v>
+        <v>3.749</v>
       </c>
       <c r="C2">
-        <v>11.108</v>
+        <v>1.975</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2">
-        <v>46283.01041666666</v>
+        <v>46285.01041666666</v>
       </c>
       <c r="B3">
-        <v>0.063</v>
+        <v>7.992</v>
       </c>
       <c r="C3">
-        <v>2.476</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2">
-        <v>46283.02083333334</v>
+        <v>46285.02083333334</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>15.319</v>
       </c>
       <c r="C4">
-        <v>11.817</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2">
-        <v>46283.03125</v>
+        <v>46285.03125</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>3.558</v>
       </c>
       <c r="C5">
-        <v>12.029</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2">
-        <v>46283.04166666666</v>
+        <v>46285.04166666666</v>
       </c>
       <c r="B6">
-        <v>2.32</v>
+        <v>10.398</v>
       </c>
       <c r="C6">
-        <v>2.637</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2">
-        <v>46283.05208333334</v>
+        <v>46285.05208333334</v>
       </c>
       <c r="B7">
-        <v>0.144</v>
+        <v>5.118</v>
       </c>
       <c r="C7">
-        <v>1.12</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2">
-        <v>46283.0625</v>
+        <v>46285.0625</v>
       </c>
       <c r="B8">
-        <v>2.646</v>
+        <v>11.953</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -477,175 +477,175 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2">
-        <v>46283.07291666666</v>
+        <v>46285.07291666666</v>
       </c>
       <c r="B9">
-        <v>3.476</v>
+        <v>16.425</v>
       </c>
       <c r="C9">
-        <v>0.5669999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2">
-        <v>46283.08333333334</v>
+        <v>46285.08333333334</v>
       </c>
       <c r="B10">
-        <v>0.001</v>
+        <v>17.146</v>
       </c>
       <c r="C10">
-        <v>7.879</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2">
-        <v>46283.09375</v>
+        <v>46285.09375</v>
       </c>
       <c r="B11">
-        <v>2.593</v>
+        <v>17.686</v>
       </c>
       <c r="C11">
-        <v>0.787</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2">
-        <v>46283.10416666666</v>
+        <v>46285.10416666666</v>
       </c>
       <c r="B12">
-        <v>0.379</v>
+        <v>3.97</v>
       </c>
       <c r="C12">
-        <v>2.317</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2">
-        <v>46283.11458333334</v>
+        <v>46285.11458333334</v>
       </c>
       <c r="B13">
-        <v>1.643</v>
+        <v>3.16</v>
       </c>
       <c r="C13">
-        <v>1.091</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2">
-        <v>46283.125</v>
+        <v>46285.125</v>
       </c>
       <c r="B14">
-        <v>0.477</v>
+        <v>0.081</v>
       </c>
       <c r="C14">
-        <v>2.528</v>
+        <v>3.984</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2">
-        <v>46283.13541666666</v>
+        <v>46285.13541666666</v>
       </c>
       <c r="B15">
-        <v>2.251</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>9.465999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2">
-        <v>46283.14583333334</v>
+        <v>46285.14583333334</v>
       </c>
       <c r="B16">
-        <v>2.045</v>
+        <v>0</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>19.647</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2">
-        <v>46283.15625</v>
+        <v>46285.15625</v>
       </c>
       <c r="B17">
-        <v>3.519</v>
+        <v>0</v>
       </c>
       <c r="C17">
-        <v>0.134</v>
+        <v>11.162</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2">
-        <v>46283.16666666666</v>
+        <v>46285.16666666666</v>
       </c>
       <c r="B18">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="C18">
-        <v>1.731</v>
+        <v>24.502</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2">
-        <v>46283.17708333334</v>
+        <v>46285.17708333334</v>
       </c>
       <c r="B19">
-        <v>1.685</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>21.609</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2">
-        <v>46283.1875</v>
+        <v>46285.1875</v>
       </c>
       <c r="B20">
-        <v>1.778</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>9.81</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2">
-        <v>46283.19791666666</v>
+        <v>46285.19791666666</v>
       </c>
       <c r="B21">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>12.251</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2">
-        <v>46283.20833333334</v>
+        <v>46285.20833333334</v>
       </c>
       <c r="B22">
-        <v>22.262</v>
+        <v>2.88</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>1.696</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2">
-        <v>46283.21875</v>
+        <v>46285.21875</v>
       </c>
       <c r="B23">
-        <v>6.94</v>
+        <v>6.001</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2">
-        <v>46283.22916666666</v>
+        <v>46285.22916666666</v>
       </c>
       <c r="B24">
-        <v>1.551</v>
+        <v>12.497</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -653,10 +653,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2">
-        <v>46283.23958333334</v>
+        <v>46285.23958333334</v>
       </c>
       <c r="B25">
-        <v>2.711</v>
+        <v>10.019</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -664,210 +664,166 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2">
-        <v>46283.25</v>
+        <v>46285.25</v>
       </c>
       <c r="B26">
-        <v>1.112</v>
+        <v>5.604</v>
       </c>
       <c r="C26">
-        <v>0.988</v>
+        <v>0.044</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2">
-        <v>46283.26041666666</v>
+        <v>46285.26041666666</v>
       </c>
       <c r="B27">
-        <v>0.5620000000000001</v>
+        <v>2.145</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>0.146</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2">
-        <v>46283.27083333334</v>
+        <v>46285.27083333334</v>
       </c>
       <c r="B28">
-        <v>1.966</v>
+        <v>0.519</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>2.356</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2">
-        <v>46283.28125</v>
+        <v>46285.28125</v>
       </c>
       <c r="B29">
-        <v>0.183</v>
+        <v>0.002</v>
       </c>
       <c r="C29">
-        <v>1.059</v>
+        <v>33.265</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2">
-        <v>46283.29166666666</v>
+        <v>46285.29166666666</v>
       </c>
       <c r="B30">
-        <v>6.221</v>
+        <v>5.573</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>0.914</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2">
-        <v>46283.30208333334</v>
+        <v>46285.30208333334</v>
       </c>
       <c r="B31">
-        <v>10.405</v>
+        <v>0.298</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>3.063</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2">
-        <v>46283.3125</v>
+        <v>46285.3125</v>
       </c>
       <c r="B32">
-        <v>13.982</v>
+        <v>0.002</v>
       </c>
       <c r="C32">
-        <v>1.869</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2">
-        <v>46283.32291666666</v>
+        <v>46285.32291666666</v>
       </c>
       <c r="B33">
         <v>0</v>
       </c>
       <c r="C33">
-        <v>37.76</v>
+        <v>3.442</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2">
-        <v>46283.33333333334</v>
+        <v>46285.33333333334</v>
       </c>
       <c r="B34">
-        <v>0.239</v>
+        <v>1.437</v>
       </c>
       <c r="C34">
-        <v>40.008</v>
+        <v>5.406</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2">
-        <v>46283.34375</v>
+        <v>46285.34375</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>13.948</v>
       </c>
       <c r="C35">
-        <v>62.967</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2">
-        <v>46283.35416666666</v>
+        <v>46285.35416666666</v>
       </c>
       <c r="B36">
-        <v>1.444</v>
+        <v>22.231</v>
       </c>
       <c r="C36">
-        <v>10.193</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2">
-        <v>46283.36458333334</v>
+        <v>46285.36458333334</v>
       </c>
       <c r="B37">
-        <v>8.275</v>
+        <v>6.957</v>
       </c>
       <c r="C37">
-        <v>0.096</v>
+        <v>0.245</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2">
-        <v>46283.375</v>
+        <v>46285.375</v>
       </c>
       <c r="B38">
-        <v>7.263</v>
+        <v>0.93</v>
       </c>
       <c r="C38">
-        <v>0.144</v>
+        <v>1.877</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="2">
-        <v>46283.38541666666</v>
+        <v>46285.38541666666</v>
       </c>
       <c r="B39">
-        <v>5.639</v>
+        <v>8.779</v>
       </c>
       <c r="C39">
-        <v>0.678</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="2">
-        <v>46283.39583333334</v>
+        <v>46285.39583333334</v>
       </c>
       <c r="B40">
-        <v>16.465</v>
+        <v>0</v>
       </c>
       <c r="C40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="2">
-        <v>46283.40625</v>
-      </c>
-      <c r="B41">
-        <v>14.093</v>
-      </c>
-      <c r="C41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="2">
-        <v>46283.41666666666</v>
-      </c>
-      <c r="B42">
-        <v>53.474</v>
-      </c>
-      <c r="C42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="2">
-        <v>46283.42708333334</v>
-      </c>
-      <c r="B43">
-        <v>29.836</v>
-      </c>
-      <c r="C43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="2">
-        <v>46283.4375</v>
-      </c>
-      <c r="B44">
-        <v>0</v>
-      </c>
-      <c r="C44">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
+++ b/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -400,76 +400,76 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2">
-        <v>46285</v>
+        <v>46295</v>
       </c>
       <c r="B2">
-        <v>3.749</v>
+        <v>11.232</v>
       </c>
       <c r="C2">
-        <v>1.975</v>
+        <v>0.135</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2">
-        <v>46285.01041666666</v>
+        <v>46295.01041666666</v>
       </c>
       <c r="B3">
-        <v>7.992</v>
+        <v>2.381</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>5.156</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2">
-        <v>46285.02083333334</v>
+        <v>46295.02083333334</v>
       </c>
       <c r="B4">
-        <v>15.319</v>
+        <v>0.2</v>
       </c>
       <c r="C4">
-        <v>0.001</v>
+        <v>4.632</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2">
-        <v>46285.03125</v>
+        <v>46295.03125</v>
       </c>
       <c r="B5">
-        <v>3.558</v>
+        <v>0.059</v>
       </c>
       <c r="C5">
-        <v>0.33</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2">
-        <v>46285.04166666666</v>
+        <v>46295.04166666666</v>
       </c>
       <c r="B6">
-        <v>10.398</v>
+        <v>8.349</v>
       </c>
       <c r="C6">
-        <v>0.058</v>
+        <v>0.171</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2">
-        <v>46285.05208333334</v>
+        <v>46295.05208333334</v>
       </c>
       <c r="B7">
-        <v>5.118</v>
+        <v>5.505</v>
       </c>
       <c r="C7">
-        <v>0.004</v>
+        <v>3.063</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2">
-        <v>46285.0625</v>
+        <v>46295.0625</v>
       </c>
       <c r="B8">
-        <v>11.953</v>
+        <v>18.212</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -477,10 +477,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2">
-        <v>46285.07291666666</v>
+        <v>46295.07291666666</v>
       </c>
       <c r="B9">
-        <v>16.425</v>
+        <v>23.351</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -488,21 +488,21 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2">
-        <v>46285.08333333334</v>
+        <v>46295.08333333334</v>
       </c>
       <c r="B10">
-        <v>17.146</v>
+        <v>5.773</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2">
-        <v>46285.09375</v>
+        <v>46295.09375</v>
       </c>
       <c r="B11">
-        <v>17.686</v>
+        <v>9.698</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -510,10 +510,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2">
-        <v>46285.10416666666</v>
+        <v>46295.10416666666</v>
       </c>
       <c r="B12">
-        <v>3.97</v>
+        <v>35.756</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -521,10 +521,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2">
-        <v>46285.11458333334</v>
+        <v>46295.11458333334</v>
       </c>
       <c r="B13">
-        <v>3.16</v>
+        <v>17.095</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -532,131 +532,131 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2">
-        <v>46285.125</v>
+        <v>46295.125</v>
       </c>
       <c r="B14">
-        <v>0.081</v>
+        <v>16.495</v>
       </c>
       <c r="C14">
-        <v>3.984</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2">
-        <v>46285.13541666666</v>
+        <v>46295.13541666666</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>19.217</v>
       </c>
       <c r="C15">
-        <v>9.465999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2">
-        <v>46285.14583333334</v>
+        <v>46295.14583333334</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>24.425</v>
       </c>
       <c r="C16">
-        <v>19.647</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2">
-        <v>46285.15625</v>
+        <v>46295.15625</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>37.883</v>
       </c>
       <c r="C17">
-        <v>11.162</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2">
-        <v>46285.16666666666</v>
+        <v>46295.16666666666</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>13.965</v>
       </c>
       <c r="C18">
-        <v>24.502</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2">
-        <v>46285.17708333334</v>
+        <v>46295.17708333334</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>9.773999999999999</v>
       </c>
       <c r="C19">
-        <v>21.609</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2">
-        <v>46285.1875</v>
+        <v>46295.1875</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>3.764</v>
       </c>
       <c r="C20">
-        <v>9.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2">
-        <v>46285.19791666666</v>
+        <v>46295.19791666666</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="C21">
-        <v>12.251</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2">
-        <v>46285.20833333334</v>
+        <v>46295.20833333334</v>
       </c>
       <c r="B22">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <v>1.696</v>
+        <v>20.298</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2">
-        <v>46285.21875</v>
+        <v>46295.21875</v>
       </c>
       <c r="B23">
-        <v>6.001</v>
+        <v>1.534</v>
       </c>
       <c r="C23">
-        <v>0.008</v>
+        <v>16.983</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2">
-        <v>46285.22916666666</v>
+        <v>46295.22916666666</v>
       </c>
       <c r="B24">
-        <v>12.497</v>
+        <v>1.335</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>0.221</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2">
-        <v>46285.23958333334</v>
+        <v>46295.23958333334</v>
       </c>
       <c r="B25">
-        <v>10.019</v>
+        <v>5.091</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -664,166 +664,188 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2">
-        <v>46285.25</v>
+        <v>46295.25</v>
       </c>
       <c r="B26">
-        <v>5.604</v>
+        <v>0.651</v>
       </c>
       <c r="C26">
-        <v>0.044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2">
-        <v>46285.26041666666</v>
+        <v>46295.26041666666</v>
       </c>
       <c r="B27">
-        <v>2.145</v>
+        <v>2.725</v>
       </c>
       <c r="C27">
-        <v>0.146</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2">
-        <v>46285.27083333334</v>
+        <v>46295.27083333334</v>
       </c>
       <c r="B28">
-        <v>0.519</v>
+        <v>30.741</v>
       </c>
       <c r="C28">
-        <v>2.356</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2">
-        <v>46285.28125</v>
+        <v>46295.28125</v>
       </c>
       <c r="B29">
-        <v>0.002</v>
+        <v>31.311</v>
       </c>
       <c r="C29">
-        <v>33.265</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2">
-        <v>46285.29166666666</v>
+        <v>46295.29166666666</v>
       </c>
       <c r="B30">
-        <v>5.573</v>
+        <v>8.467000000000001</v>
       </c>
       <c r="C30">
-        <v>0.914</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2">
-        <v>46285.30208333334</v>
+        <v>46295.30208333334</v>
       </c>
       <c r="B31">
-        <v>0.298</v>
+        <v>11.85</v>
       </c>
       <c r="C31">
-        <v>3.063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2">
-        <v>46285.3125</v>
+        <v>46295.3125</v>
       </c>
       <c r="B32">
-        <v>0.002</v>
+        <v>13.605</v>
       </c>
       <c r="C32">
-        <v>2.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2">
-        <v>46285.32291666666</v>
+        <v>46295.32291666666</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>8.571999999999999</v>
       </c>
       <c r="C33">
-        <v>3.442</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2">
-        <v>46285.33333333334</v>
+        <v>46295.33333333334</v>
       </c>
       <c r="B34">
-        <v>1.437</v>
+        <v>26.704</v>
       </c>
       <c r="C34">
-        <v>5.406</v>
+        <v>0.151</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2">
-        <v>46285.34375</v>
+        <v>46295.34375</v>
       </c>
       <c r="B35">
-        <v>13.948</v>
+        <v>21.107</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>0.073</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2">
-        <v>46285.35416666666</v>
+        <v>46295.35416666666</v>
       </c>
       <c r="B36">
-        <v>22.231</v>
+        <v>4.749</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>0.237</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2">
-        <v>46285.36458333334</v>
+        <v>46295.36458333334</v>
       </c>
       <c r="B37">
-        <v>6.957</v>
+        <v>0.864</v>
       </c>
       <c r="C37">
-        <v>0.245</v>
+        <v>14.357</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2">
-        <v>46285.375</v>
+        <v>46295.375</v>
       </c>
       <c r="B38">
-        <v>0.93</v>
+        <v>7.365</v>
       </c>
       <c r="C38">
-        <v>1.877</v>
+        <v>0.044</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="2">
-        <v>46285.38541666666</v>
+        <v>46295.38541666666</v>
       </c>
       <c r="B39">
-        <v>8.779</v>
+        <v>0.323</v>
       </c>
       <c r="C39">
-        <v>0.025</v>
+        <v>8.962</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="2">
-        <v>46285.39583333334</v>
+        <v>46295.39583333334</v>
       </c>
       <c r="B40">
         <v>0</v>
       </c>
       <c r="C40">
+        <v>8.558</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="2">
+        <v>46295.40625</v>
+      </c>
+      <c r="B41">
+        <v>0</v>
+      </c>
+      <c r="C41">
+        <v>50.093</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="2">
+        <v>46295.41666666666</v>
+      </c>
+      <c r="B42">
+        <v>0</v>
+      </c>
+      <c r="C42">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
+++ b/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -400,76 +400,76 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2">
-        <v>46295</v>
+        <v>46298</v>
       </c>
       <c r="B2">
-        <v>11.232</v>
+        <v>0.652</v>
       </c>
       <c r="C2">
-        <v>0.135</v>
+        <v>17.199</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2">
-        <v>46295.01041666666</v>
+        <v>46298.01041666666</v>
       </c>
       <c r="B3">
-        <v>2.381</v>
+        <v>0.163</v>
       </c>
       <c r="C3">
-        <v>5.156</v>
+        <v>2.254</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2">
-        <v>46295.02083333334</v>
+        <v>46298.02083333334</v>
       </c>
       <c r="B4">
-        <v>0.2</v>
+        <v>0.012</v>
       </c>
       <c r="C4">
-        <v>4.632</v>
+        <v>6.333</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2">
-        <v>46295.03125</v>
+        <v>46298.03125</v>
       </c>
       <c r="B5">
-        <v>0.059</v>
+        <v>0.194</v>
       </c>
       <c r="C5">
-        <v>2.1</v>
+        <v>6.11</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2">
-        <v>46295.04166666666</v>
+        <v>46298.04166666666</v>
       </c>
       <c r="B6">
-        <v>8.349</v>
+        <v>0.194</v>
       </c>
       <c r="C6">
-        <v>0.171</v>
+        <v>1.091</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2">
-        <v>46295.05208333334</v>
+        <v>46298.05208333334</v>
       </c>
       <c r="B7">
-        <v>5.505</v>
+        <v>6.123</v>
       </c>
       <c r="C7">
-        <v>3.063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2">
-        <v>46295.0625</v>
+        <v>46298.0625</v>
       </c>
       <c r="B8">
-        <v>18.212</v>
+        <v>24.362</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -477,32 +477,32 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2">
-        <v>46295.07291666666</v>
+        <v>46298.07291666666</v>
       </c>
       <c r="B9">
-        <v>23.351</v>
+        <v>0.083</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>7.733</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2">
-        <v>46295.08333333334</v>
+        <v>46298.08333333334</v>
       </c>
       <c r="B10">
-        <v>5.773</v>
+        <v>1.988</v>
       </c>
       <c r="C10">
-        <v>0.028</v>
+        <v>0.478</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2">
-        <v>46295.09375</v>
+        <v>46298.09375</v>
       </c>
       <c r="B11">
-        <v>9.698</v>
+        <v>9.561999999999999</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -510,43 +510,43 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2">
-        <v>46295.10416666666</v>
+        <v>46298.10416666666</v>
       </c>
       <c r="B12">
-        <v>35.756</v>
+        <v>5.239</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2">
-        <v>46295.11458333334</v>
+        <v>46298.11458333334</v>
       </c>
       <c r="B13">
-        <v>17.095</v>
+        <v>0.258</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>5.357</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2">
-        <v>46295.125</v>
+        <v>46298.125</v>
       </c>
       <c r="B14">
-        <v>16.495</v>
+        <v>4.864</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2">
-        <v>46295.13541666666</v>
+        <v>46298.13541666666</v>
       </c>
       <c r="B15">
-        <v>19.217</v>
+        <v>3.905</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -554,10 +554,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2">
-        <v>46295.14583333334</v>
+        <v>46298.14583333334</v>
       </c>
       <c r="B16">
-        <v>24.425</v>
+        <v>6.35</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -565,10 +565,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2">
-        <v>46295.15625</v>
+        <v>46298.15625</v>
       </c>
       <c r="B17">
-        <v>37.883</v>
+        <v>10.297</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -576,10 +576,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2">
-        <v>46295.16666666666</v>
+        <v>46298.16666666666</v>
       </c>
       <c r="B18">
-        <v>13.965</v>
+        <v>17.226</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -587,265 +587,210 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2">
-        <v>46295.17708333334</v>
+        <v>46298.17708333334</v>
       </c>
       <c r="B19">
-        <v>9.773999999999999</v>
+        <v>1.975</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2">
-        <v>46295.1875</v>
+        <v>46298.1875</v>
       </c>
       <c r="B20">
-        <v>3.764</v>
+        <v>3.482</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>1.343</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2">
-        <v>46295.19791666666</v>
+        <v>46298.19791666666</v>
       </c>
       <c r="B21">
-        <v>4.44</v>
+        <v>27.439</v>
       </c>
       <c r="C21">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2">
-        <v>46295.20833333334</v>
+        <v>46298.20833333334</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>1.444</v>
       </c>
       <c r="C22">
-        <v>20.298</v>
+        <v>0.894</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2">
-        <v>46295.21875</v>
+        <v>46298.21875</v>
       </c>
       <c r="B23">
-        <v>1.534</v>
+        <v>5.032</v>
       </c>
       <c r="C23">
-        <v>16.983</v>
+        <v>0.288</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2">
-        <v>46295.22916666666</v>
+        <v>46298.22916666666</v>
       </c>
       <c r="B24">
-        <v>1.335</v>
+        <v>0.026</v>
       </c>
       <c r="C24">
-        <v>0.221</v>
+        <v>6.864</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2">
-        <v>46295.23958333334</v>
+        <v>46298.23958333334</v>
       </c>
       <c r="B25">
-        <v>5.091</v>
+        <v>0.197</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>7.578</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2">
-        <v>46295.25</v>
+        <v>46298.25</v>
       </c>
       <c r="B26">
-        <v>0.651</v>
+        <v>1.562</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>0.641</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2">
-        <v>46295.26041666666</v>
+        <v>46298.26041666666</v>
       </c>
       <c r="B27">
-        <v>2.725</v>
+        <v>0.804</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>0.664</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2">
-        <v>46295.27083333334</v>
+        <v>46298.27083333334</v>
       </c>
       <c r="B28">
-        <v>30.741</v>
+        <v>0.252</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>0.212</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2">
-        <v>46295.28125</v>
+        <v>46298.28125</v>
       </c>
       <c r="B29">
-        <v>31.311</v>
+        <v>0.098</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>5.581</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2">
-        <v>46295.29166666666</v>
+        <v>46298.29166666666</v>
       </c>
       <c r="B30">
-        <v>8.467000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>6.278</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2">
-        <v>46295.30208333334</v>
+        <v>46298.30208333334</v>
       </c>
       <c r="B31">
-        <v>11.85</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>13.374</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2">
-        <v>46295.3125</v>
+        <v>46298.3125</v>
       </c>
       <c r="B32">
-        <v>13.605</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2">
-        <v>46295.32291666666</v>
+        <v>46298.32291666666</v>
       </c>
       <c r="B33">
-        <v>8.571999999999999</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <v>0.01</v>
+        <v>5.379</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2">
-        <v>46295.33333333334</v>
+        <v>46298.33333333334</v>
       </c>
       <c r="B34">
-        <v>26.704</v>
+        <v>0.046</v>
       </c>
       <c r="C34">
-        <v>0.151</v>
+        <v>12.133</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2">
-        <v>46295.34375</v>
+        <v>46298.34375</v>
       </c>
       <c r="B35">
-        <v>21.107</v>
+        <v>0</v>
       </c>
       <c r="C35">
-        <v>0.073</v>
+        <v>13.566</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2">
-        <v>46295.35416666666</v>
+        <v>46298.35416666666</v>
       </c>
       <c r="B36">
-        <v>4.749</v>
+        <v>2.73</v>
       </c>
       <c r="C36">
-        <v>0.237</v>
+        <v>8.824</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2">
-        <v>46295.36458333334</v>
+        <v>46298.36458333334</v>
       </c>
       <c r="B37">
-        <v>0.864</v>
+        <v>0</v>
       </c>
       <c r="C37">
-        <v>14.357</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="2">
-        <v>46295.375</v>
-      </c>
-      <c r="B38">
-        <v>7.365</v>
-      </c>
-      <c r="C38">
-        <v>0.044</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="2">
-        <v>46295.38541666666</v>
-      </c>
-      <c r="B39">
-        <v>0.323</v>
-      </c>
-      <c r="C39">
-        <v>8.962</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="2">
-        <v>46295.39583333334</v>
-      </c>
-      <c r="B40">
-        <v>0</v>
-      </c>
-      <c r="C40">
-        <v>8.558</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="2">
-        <v>46295.40625</v>
-      </c>
-      <c r="B41">
-        <v>0</v>
-      </c>
-      <c r="C41">
-        <v>50.093</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="2">
-        <v>46295.41666666666</v>
-      </c>
-      <c r="B42">
-        <v>0</v>
-      </c>
-      <c r="C42">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
+++ b/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
@@ -400,392 +400,392 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="B2">
-        <v>0.652</v>
+        <v>1.587</v>
       </c>
       <c r="C2">
-        <v>17.199</v>
+        <v>3.278</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2">
-        <v>46298.01041666666</v>
+        <v>46299.01041666666</v>
       </c>
       <c r="B3">
-        <v>0.163</v>
+        <v>0.393</v>
       </c>
       <c r="C3">
-        <v>2.254</v>
+        <v>1.164</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2">
-        <v>46298.02083333334</v>
+        <v>46299.02083333334</v>
       </c>
       <c r="B4">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>6.333</v>
+        <v>16.213</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2">
-        <v>46298.03125</v>
+        <v>46299.03125</v>
       </c>
       <c r="B5">
-        <v>0.194</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>6.11</v>
+        <v>2.089</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2">
-        <v>46298.04166666666</v>
+        <v>46299.04166666666</v>
       </c>
       <c r="B6">
-        <v>0.194</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>1.091</v>
+        <v>10.687</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2">
-        <v>46298.05208333334</v>
+        <v>46299.05208333334</v>
       </c>
       <c r="B7">
-        <v>6.123</v>
+        <v>0.005</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2">
-        <v>46298.0625</v>
+        <v>46299.0625</v>
       </c>
       <c r="B8">
-        <v>24.362</v>
+        <v>0.111</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2">
-        <v>46298.07291666666</v>
+        <v>46299.07291666666</v>
       </c>
       <c r="B9">
-        <v>0.083</v>
+        <v>2.265</v>
       </c>
       <c r="C9">
-        <v>7.733</v>
+        <v>0.336</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2">
-        <v>46298.08333333334</v>
+        <v>46299.08333333334</v>
       </c>
       <c r="B10">
-        <v>1.988</v>
+        <v>1.148</v>
       </c>
       <c r="C10">
-        <v>0.478</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2">
-        <v>46298.09375</v>
+        <v>46299.09375</v>
       </c>
       <c r="B11">
-        <v>9.561999999999999</v>
+        <v>0.011</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>1.815</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2">
-        <v>46298.10416666666</v>
+        <v>46299.10416666666</v>
       </c>
       <c r="B12">
-        <v>5.239</v>
+        <v>5.225</v>
       </c>
       <c r="C12">
-        <v>1.188</v>
+        <v>1.064</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2">
-        <v>46298.11458333334</v>
+        <v>46299.11458333334</v>
       </c>
       <c r="B13">
-        <v>0.258</v>
+        <v>16.84</v>
       </c>
       <c r="C13">
-        <v>5.357</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2">
-        <v>46298.125</v>
+        <v>46299.125</v>
       </c>
       <c r="B14">
-        <v>4.864</v>
+        <v>2.652</v>
       </c>
       <c r="C14">
-        <v>0.11</v>
+        <v>0.668</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2">
-        <v>46298.13541666666</v>
+        <v>46299.13541666666</v>
       </c>
       <c r="B15">
-        <v>3.905</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>6.414</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2">
-        <v>46298.14583333334</v>
+        <v>46299.14583333334</v>
       </c>
       <c r="B16">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>14.424</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2">
-        <v>46298.15625</v>
+        <v>46299.15625</v>
       </c>
       <c r="B17">
-        <v>10.297</v>
+        <v>0.139</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>5.822</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2">
-        <v>46298.16666666666</v>
+        <v>46299.16666666666</v>
       </c>
       <c r="B18">
-        <v>17.226</v>
+        <v>0</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>36.419</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2">
-        <v>46298.17708333334</v>
+        <v>46299.17708333334</v>
       </c>
       <c r="B19">
-        <v>1.975</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>2.36</v>
+        <v>32.733</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2">
-        <v>46298.1875</v>
+        <v>46299.1875</v>
       </c>
       <c r="B20">
-        <v>3.482</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>1.343</v>
+        <v>16.529</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2">
-        <v>46298.19791666666</v>
+        <v>46299.19791666666</v>
       </c>
       <c r="B21">
-        <v>27.439</v>
+        <v>0.001</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>11.421</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2">
-        <v>46298.20833333334</v>
+        <v>46299.20833333334</v>
       </c>
       <c r="B22">
-        <v>1.444</v>
+        <v>0.092</v>
       </c>
       <c r="C22">
-        <v>0.894</v>
+        <v>5.766</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2">
-        <v>46298.21875</v>
+        <v>46299.21875</v>
       </c>
       <c r="B23">
-        <v>5.032</v>
+        <v>0.127</v>
       </c>
       <c r="C23">
-        <v>0.288</v>
+        <v>0.9379999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2">
-        <v>46298.22916666666</v>
+        <v>46299.22916666666</v>
       </c>
       <c r="B24">
-        <v>0.026</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>6.864</v>
+        <v>6.792</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2">
-        <v>46298.23958333334</v>
+        <v>46299.23958333334</v>
       </c>
       <c r="B25">
-        <v>0.197</v>
+        <v>1.711</v>
       </c>
       <c r="C25">
-        <v>7.578</v>
+        <v>1.143</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2">
-        <v>46298.25</v>
+        <v>46299.25</v>
       </c>
       <c r="B26">
-        <v>1.562</v>
+        <v>0.094</v>
       </c>
       <c r="C26">
-        <v>0.641</v>
+        <v>6.401</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2">
-        <v>46298.26041666666</v>
+        <v>46299.26041666666</v>
       </c>
       <c r="B27">
-        <v>0.804</v>
+        <v>0.171</v>
       </c>
       <c r="C27">
-        <v>0.664</v>
+        <v>4.978</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2">
-        <v>46298.27083333334</v>
+        <v>46299.27083333334</v>
       </c>
       <c r="B28">
-        <v>0.252</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>0.212</v>
+        <v>3.003</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2">
-        <v>46298.28125</v>
+        <v>46299.28125</v>
       </c>
       <c r="B29">
-        <v>0.098</v>
+        <v>6.469</v>
       </c>
       <c r="C29">
-        <v>5.581</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2">
-        <v>46298.29166666666</v>
+        <v>46299.29166666666</v>
       </c>
       <c r="B30">
-        <v>0.01</v>
+        <v>8.956</v>
       </c>
       <c r="C30">
-        <v>6.278</v>
+        <v>0.244</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2">
-        <v>46298.30208333334</v>
+        <v>46299.30208333334</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>0.746</v>
       </c>
       <c r="C31">
-        <v>13.374</v>
+        <v>1.751</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2">
-        <v>46298.3125</v>
+        <v>46299.3125</v>
       </c>
       <c r="B32">
         <v>0</v>
       </c>
       <c r="C32">
-        <v>5.88</v>
+        <v>2.314</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2">
-        <v>46298.32291666666</v>
+        <v>46299.32291666666</v>
       </c>
       <c r="B33">
         <v>0</v>
       </c>
       <c r="C33">
-        <v>5.379</v>
+        <v>7.864</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2">
-        <v>46298.33333333334</v>
+        <v>46299.33333333334</v>
       </c>
       <c r="B34">
-        <v>0.046</v>
+        <v>4.515</v>
       </c>
       <c r="C34">
-        <v>12.133</v>
+        <v>1.387</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2">
-        <v>46298.34375</v>
+        <v>46299.34375</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>15.502</v>
       </c>
       <c r="C35">
-        <v>13.566</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2">
-        <v>46298.35416666666</v>
+        <v>46299.35416666666</v>
       </c>
       <c r="B36">
-        <v>2.73</v>
+        <v>21.309</v>
       </c>
       <c r="C36">
-        <v>8.824</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2">
-        <v>46298.36458333334</v>
+        <v>46299.36458333334</v>
       </c>
       <c r="B37">
         <v>0</v>

--- a/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
+++ b/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -400,131 +400,131 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="B2">
-        <v>1.587</v>
+        <v>5.027</v>
       </c>
       <c r="C2">
-        <v>3.278</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2">
-        <v>46299.01041666666</v>
+        <v>46300.01041666666</v>
       </c>
       <c r="B3">
-        <v>0.393</v>
+        <v>20.872</v>
       </c>
       <c r="C3">
-        <v>1.164</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2">
-        <v>46299.02083333334</v>
+        <v>46300.02083333334</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>29.031</v>
       </c>
       <c r="C4">
-        <v>16.213</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2">
-        <v>46299.03125</v>
+        <v>46300.03125</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>5.212</v>
       </c>
       <c r="C5">
-        <v>2.089</v>
+        <v>0.392</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2">
-        <v>46299.04166666666</v>
+        <v>46300.04166666666</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>0.109</v>
       </c>
       <c r="C6">
-        <v>10.687</v>
+        <v>6.134</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2">
-        <v>46299.05208333334</v>
+        <v>46300.05208333334</v>
       </c>
       <c r="B7">
-        <v>0.005</v>
+        <v>0.028</v>
       </c>
       <c r="C7">
-        <v>2.31</v>
+        <v>6.462</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2">
-        <v>46299.0625</v>
+        <v>46300.0625</v>
       </c>
       <c r="B8">
-        <v>0.111</v>
+        <v>0.598</v>
       </c>
       <c r="C8">
-        <v>8.75</v>
+        <v>6.214</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2">
-        <v>46299.07291666666</v>
+        <v>46300.07291666666</v>
       </c>
       <c r="B9">
-        <v>2.265</v>
+        <v>1.036</v>
       </c>
       <c r="C9">
-        <v>0.336</v>
+        <v>0.403</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2">
-        <v>46299.08333333334</v>
+        <v>46300.08333333334</v>
       </c>
       <c r="B10">
-        <v>1.148</v>
+        <v>1.39</v>
       </c>
       <c r="C10">
-        <v>3.04</v>
+        <v>5.391</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2">
-        <v>46299.09375</v>
+        <v>46300.09375</v>
       </c>
       <c r="B11">
-        <v>0.011</v>
+        <v>0.226</v>
       </c>
       <c r="C11">
-        <v>1.815</v>
+        <v>5.294</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2">
-        <v>46299.10416666666</v>
+        <v>46300.10416666666</v>
       </c>
       <c r="B12">
-        <v>5.225</v>
+        <v>1.35</v>
       </c>
       <c r="C12">
-        <v>1.064</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2">
-        <v>46299.11458333334</v>
+        <v>46300.11458333334</v>
       </c>
       <c r="B13">
-        <v>16.84</v>
+        <v>9.911</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -532,265 +532,485 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2">
-        <v>46299.125</v>
+        <v>46300.125</v>
       </c>
       <c r="B14">
-        <v>2.652</v>
+        <v>2.902</v>
       </c>
       <c r="C14">
-        <v>0.668</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2">
-        <v>46299.13541666666</v>
+        <v>46300.13541666666</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>2.731</v>
       </c>
       <c r="C15">
-        <v>6.414</v>
+        <v>0.074</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2">
-        <v>46299.14583333334</v>
+        <v>46300.14583333334</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>6.442</v>
       </c>
       <c r="C16">
-        <v>14.424</v>
+        <v>0.082</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2">
-        <v>46299.15625</v>
+        <v>46300.15625</v>
       </c>
       <c r="B17">
-        <v>0.139</v>
+        <v>9.206</v>
       </c>
       <c r="C17">
-        <v>5.822</v>
+        <v>0.172</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2">
-        <v>46299.16666666666</v>
+        <v>46300.16666666666</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>0.554</v>
       </c>
       <c r="C18">
-        <v>36.419</v>
+        <v>2.093</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2">
-        <v>46299.17708333334</v>
+        <v>46300.17708333334</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>3.812</v>
       </c>
       <c r="C19">
-        <v>32.733</v>
+        <v>0.038</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2">
-        <v>46299.1875</v>
+        <v>46300.1875</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>1.053</v>
       </c>
       <c r="C20">
-        <v>16.529</v>
+        <v>2.029</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2">
-        <v>46299.19791666666</v>
+        <v>46300.19791666666</v>
       </c>
       <c r="B21">
-        <v>0.001</v>
+        <v>18.835</v>
       </c>
       <c r="C21">
-        <v>11.421</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2">
-        <v>46299.20833333334</v>
+        <v>46300.20833333334</v>
       </c>
       <c r="B22">
-        <v>0.092</v>
+        <v>4.088</v>
       </c>
       <c r="C22">
-        <v>5.766</v>
+        <v>0.739</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2">
-        <v>46299.21875</v>
+        <v>46300.21875</v>
       </c>
       <c r="B23">
-        <v>0.127</v>
+        <v>0.789</v>
       </c>
       <c r="C23">
-        <v>0.9379999999999999</v>
+        <v>1.482</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2">
-        <v>46299.22916666666</v>
+        <v>46300.22916666666</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>1.358</v>
       </c>
       <c r="C24">
-        <v>6.792</v>
+        <v>0.521</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2">
-        <v>46299.23958333334</v>
+        <v>46300.23958333334</v>
       </c>
       <c r="B25">
-        <v>1.711</v>
+        <v>6.234</v>
       </c>
       <c r="C25">
-        <v>1.143</v>
+        <v>1.807</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2">
-        <v>46299.25</v>
+        <v>46300.25</v>
       </c>
       <c r="B26">
-        <v>0.094</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <v>6.401</v>
+        <v>17.478</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2">
-        <v>46299.26041666666</v>
+        <v>46300.26041666666</v>
       </c>
       <c r="B27">
-        <v>0.171</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>4.978</v>
+        <v>21.773</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2">
-        <v>46299.27083333334</v>
+        <v>46300.27083333334</v>
       </c>
       <c r="B28">
         <v>0</v>
       </c>
       <c r="C28">
-        <v>3.003</v>
+        <v>11.804</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2">
-        <v>46299.28125</v>
+        <v>46300.28125</v>
       </c>
       <c r="B29">
-        <v>6.469</v>
+        <v>0.231</v>
       </c>
       <c r="C29">
-        <v>0.113</v>
+        <v>7.103</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2">
-        <v>46299.29166666666</v>
+        <v>46300.29166666666</v>
       </c>
       <c r="B30">
-        <v>8.956</v>
+        <v>0.22</v>
       </c>
       <c r="C30">
-        <v>0.244</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2">
-        <v>46299.30208333334</v>
+        <v>46300.30208333334</v>
       </c>
       <c r="B31">
-        <v>0.746</v>
+        <v>0.082</v>
       </c>
       <c r="C31">
-        <v>1.751</v>
+        <v>9.285</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2">
-        <v>46299.3125</v>
+        <v>46300.3125</v>
       </c>
       <c r="B32">
         <v>0</v>
       </c>
       <c r="C32">
-        <v>2.314</v>
+        <v>7.333</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2">
-        <v>46299.32291666666</v>
+        <v>46300.32291666666</v>
       </c>
       <c r="B33">
         <v>0</v>
       </c>
       <c r="C33">
-        <v>7.864</v>
+        <v>11.973</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2">
-        <v>46299.33333333334</v>
+        <v>46300.33333333334</v>
       </c>
       <c r="B34">
-        <v>4.515</v>
+        <v>0</v>
       </c>
       <c r="C34">
-        <v>1.387</v>
+        <v>23.741</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2">
-        <v>46299.34375</v>
+        <v>46300.34375</v>
       </c>
       <c r="B35">
-        <v>15.502</v>
+        <v>0</v>
       </c>
       <c r="C35">
-        <v>0.001</v>
+        <v>21.955</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2">
-        <v>46299.35416666666</v>
+        <v>46300.35416666666</v>
       </c>
       <c r="B36">
-        <v>21.309</v>
+        <v>0</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>16.534</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2">
-        <v>46299.36458333334</v>
+        <v>46300.36458333334</v>
       </c>
       <c r="B37">
         <v>0</v>
       </c>
       <c r="C37">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="2">
+        <v>46300.375</v>
+      </c>
+      <c r="B38">
+        <v>15.217</v>
+      </c>
+      <c r="C38">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="2">
+        <v>46300.38541666666</v>
+      </c>
+      <c r="B39">
+        <v>2.842</v>
+      </c>
+      <c r="C39">
+        <v>0.826</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="2">
+        <v>46300.39583333334</v>
+      </c>
+      <c r="B40">
+        <v>1.365</v>
+      </c>
+      <c r="C40">
+        <v>0.858</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="2">
+        <v>46300.40625</v>
+      </c>
+      <c r="B41">
+        <v>4.933</v>
+      </c>
+      <c r="C41">
+        <v>0.585</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="2">
+        <v>46300.41666666666</v>
+      </c>
+      <c r="B42">
+        <v>21.638</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="2">
+        <v>46300.42708333334</v>
+      </c>
+      <c r="B43">
+        <v>14.528</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="2">
+        <v>46300.4375</v>
+      </c>
+      <c r="B44">
+        <v>2.661</v>
+      </c>
+      <c r="C44">
+        <v>7.552</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="2">
+        <v>46300.44791666666</v>
+      </c>
+      <c r="B45">
+        <v>0.023</v>
+      </c>
+      <c r="C45">
+        <v>26.068</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="2">
+        <v>46300.45833333334</v>
+      </c>
+      <c r="B46">
+        <v>0</v>
+      </c>
+      <c r="C46">
+        <v>9.917999999999999</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="2">
+        <v>46300.46875</v>
+      </c>
+      <c r="B47">
+        <v>0.595</v>
+      </c>
+      <c r="C47">
+        <v>12.207</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="2">
+        <v>46300.47916666666</v>
+      </c>
+      <c r="B48">
+        <v>0.6</v>
+      </c>
+      <c r="C48">
+        <v>10.039</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="2">
+        <v>46300.48958333334</v>
+      </c>
+      <c r="B49">
+        <v>1.069</v>
+      </c>
+      <c r="C49">
+        <v>2.162</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="2">
+        <v>46300.5</v>
+      </c>
+      <c r="B50">
+        <v>0</v>
+      </c>
+      <c r="C50">
+        <v>2.425</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="2">
+        <v>46300.51041666666</v>
+      </c>
+      <c r="B51">
+        <v>0</v>
+      </c>
+      <c r="C51">
+        <v>17.135</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="2">
+        <v>46300.52083333334</v>
+      </c>
+      <c r="B52">
+        <v>0</v>
+      </c>
+      <c r="C52">
+        <v>3.117</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="2">
+        <v>46300.53125</v>
+      </c>
+      <c r="B53">
+        <v>3</v>
+      </c>
+      <c r="C53">
+        <v>1.124</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="2">
+        <v>46300.54166666666</v>
+      </c>
+      <c r="B54">
+        <v>1.153</v>
+      </c>
+      <c r="C54">
+        <v>1.686</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" s="2">
+        <v>46300.55208333334</v>
+      </c>
+      <c r="B55">
+        <v>0.162</v>
+      </c>
+      <c r="C55">
+        <v>1.701</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" s="2">
+        <v>46300.5625</v>
+      </c>
+      <c r="B56">
+        <v>0</v>
+      </c>
+      <c r="C56">
+        <v>9.475</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" s="2">
+        <v>46300.57291666666</v>
+      </c>
+      <c r="B57">
+        <v>0</v>
+      </c>
+      <c r="C57">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
+++ b/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -400,21 +400,21 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2">
-        <v>46300</v>
+        <v>46307</v>
       </c>
       <c r="B2">
-        <v>5.027</v>
+        <v>44.359</v>
       </c>
       <c r="C2">
-        <v>0.005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2">
-        <v>46300.01041666666</v>
+        <v>46307.01041666666</v>
       </c>
       <c r="B3">
-        <v>20.872</v>
+        <v>37.504</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -422,10 +422,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2">
-        <v>46300.02083333334</v>
+        <v>46307.02083333334</v>
       </c>
       <c r="B4">
-        <v>29.031</v>
+        <v>15.403</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -433,584 +433,419 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2">
-        <v>46300.03125</v>
+        <v>46307.03125</v>
       </c>
       <c r="B5">
-        <v>5.212</v>
+        <v>0.275</v>
       </c>
       <c r="C5">
-        <v>0.392</v>
+        <v>12.517</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2">
-        <v>46300.04166666666</v>
+        <v>46307.04166666666</v>
       </c>
       <c r="B6">
-        <v>0.109</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>6.134</v>
+        <v>42.629</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2">
-        <v>46300.05208333334</v>
+        <v>46307.05208333334</v>
       </c>
       <c r="B7">
-        <v>0.028</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>6.462</v>
+        <v>32.285</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2">
-        <v>46300.0625</v>
+        <v>46307.0625</v>
       </c>
       <c r="B8">
-        <v>0.598</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>6.214</v>
+        <v>63.343</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2">
-        <v>46300.07291666666</v>
+        <v>46307.07291666666</v>
       </c>
       <c r="B9">
-        <v>1.036</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>0.403</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2">
-        <v>46300.08333333334</v>
+        <v>46307.08333333334</v>
       </c>
       <c r="B10">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>5.391</v>
+        <v>34.317</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2">
-        <v>46300.09375</v>
+        <v>46307.09375</v>
       </c>
       <c r="B11">
-        <v>0.226</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>5.294</v>
+        <v>3.607</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2">
-        <v>46300.10416666666</v>
+        <v>46307.10416666666</v>
       </c>
       <c r="B12">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>0.012</v>
+        <v>29.434</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2">
-        <v>46300.11458333334</v>
+        <v>46307.11458333334</v>
       </c>
       <c r="B13">
-        <v>9.911</v>
+        <v>0.019</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>8.378</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2">
-        <v>46300.125</v>
+        <v>46307.125</v>
       </c>
       <c r="B14">
-        <v>2.902</v>
+        <v>0</v>
       </c>
       <c r="C14">
-        <v>0.46</v>
+        <v>7.337</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2">
-        <v>46300.13541666666</v>
+        <v>46307.13541666666</v>
       </c>
       <c r="B15">
-        <v>2.731</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <v>0.074</v>
+        <v>1.625</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2">
-        <v>46300.14583333334</v>
+        <v>46307.14583333334</v>
       </c>
       <c r="B16">
-        <v>6.442</v>
+        <v>0</v>
       </c>
       <c r="C16">
-        <v>0.082</v>
+        <v>3.989</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2">
-        <v>46300.15625</v>
+        <v>46307.15625</v>
       </c>
       <c r="B17">
-        <v>9.206</v>
+        <v>0</v>
       </c>
       <c r="C17">
-        <v>0.172</v>
+        <v>22.469</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2">
-        <v>46300.16666666666</v>
+        <v>46307.16666666666</v>
       </c>
       <c r="B18">
-        <v>0.554</v>
+        <v>0</v>
       </c>
       <c r="C18">
-        <v>2.093</v>
+        <v>19.057</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2">
-        <v>46300.17708333334</v>
+        <v>46307.17708333334</v>
       </c>
       <c r="B19">
-        <v>3.812</v>
+        <v>2.563</v>
       </c>
       <c r="C19">
-        <v>0.038</v>
+        <v>2.735</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2">
-        <v>46300.1875</v>
+        <v>46307.1875</v>
       </c>
       <c r="B20">
-        <v>1.053</v>
+        <v>6.725</v>
       </c>
       <c r="C20">
-        <v>2.029</v>
+        <v>0.053</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2">
-        <v>46300.19791666666</v>
+        <v>46307.19791666666</v>
       </c>
       <c r="B21">
-        <v>18.835</v>
+        <v>5.557</v>
       </c>
       <c r="C21">
-        <v>0.05</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2">
-        <v>46300.20833333334</v>
+        <v>46307.20833333334</v>
       </c>
       <c r="B22">
-        <v>4.088</v>
+        <v>2.568</v>
       </c>
       <c r="C22">
-        <v>0.739</v>
+        <v>12.933</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2">
-        <v>46300.21875</v>
+        <v>46307.21875</v>
       </c>
       <c r="B23">
-        <v>0.789</v>
+        <v>0.004</v>
       </c>
       <c r="C23">
-        <v>1.482</v>
+        <v>12.166</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2">
-        <v>46300.22916666666</v>
+        <v>46307.22916666666</v>
       </c>
       <c r="B24">
-        <v>1.358</v>
+        <v>2.081</v>
       </c>
       <c r="C24">
-        <v>0.521</v>
+        <v>0.748</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2">
-        <v>46300.23958333334</v>
+        <v>46307.23958333334</v>
       </c>
       <c r="B25">
-        <v>6.234</v>
+        <v>15.296</v>
       </c>
       <c r="C25">
-        <v>1.807</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2">
-        <v>46300.25</v>
+        <v>46307.25</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>11.418</v>
       </c>
       <c r="C26">
-        <v>17.478</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2">
-        <v>46300.26041666666</v>
+        <v>46307.26041666666</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>0.917</v>
       </c>
       <c r="C27">
-        <v>21.773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2">
-        <v>46300.27083333334</v>
+        <v>46307.27083333334</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>2.033</v>
       </c>
       <c r="C28">
-        <v>11.804</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2">
-        <v>46300.28125</v>
+        <v>46307.28125</v>
       </c>
       <c r="B29">
-        <v>0.231</v>
+        <v>3.496</v>
       </c>
       <c r="C29">
-        <v>7.103</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2">
-        <v>46300.29166666666</v>
+        <v>46307.29166666666</v>
       </c>
       <c r="B30">
-        <v>0.22</v>
+        <v>14.085</v>
       </c>
       <c r="C30">
-        <v>1.51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2">
-        <v>46300.30208333334</v>
+        <v>46307.30208333334</v>
       </c>
       <c r="B31">
-        <v>0.082</v>
+        <v>2.808</v>
       </c>
       <c r="C31">
-        <v>9.285</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2">
-        <v>46300.3125</v>
+        <v>46307.3125</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>0.157</v>
       </c>
       <c r="C32">
-        <v>7.333</v>
+        <v>0.122</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2">
-        <v>46300.32291666666</v>
+        <v>46307.32291666666</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="C33">
-        <v>11.973</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2">
-        <v>46300.33333333334</v>
+        <v>46307.33333333334</v>
       </c>
       <c r="B34">
         <v>0</v>
       </c>
       <c r="C34">
-        <v>23.741</v>
+        <v>37.099</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2">
-        <v>46300.34375</v>
+        <v>46307.34375</v>
       </c>
       <c r="B35">
         <v>0</v>
       </c>
       <c r="C35">
-        <v>21.955</v>
+        <v>23.986</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2">
-        <v>46300.35416666666</v>
+        <v>46307.35416666666</v>
       </c>
       <c r="B36">
         <v>0</v>
       </c>
       <c r="C36">
-        <v>16.534</v>
+        <v>9.470000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2">
-        <v>46300.36458333334</v>
+        <v>46307.36458333334</v>
       </c>
       <c r="B37">
         <v>0</v>
       </c>
       <c r="C37">
-        <v>1.21</v>
+        <v>19.004</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2">
-        <v>46300.375</v>
+        <v>46307.375</v>
       </c>
       <c r="B38">
-        <v>15.217</v>
+        <v>0.021</v>
       </c>
       <c r="C38">
-        <v>0.005</v>
+        <v>5.716</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="2">
-        <v>46300.38541666666</v>
+        <v>46307.38541666666</v>
       </c>
       <c r="B39">
-        <v>2.842</v>
+        <v>8.93</v>
       </c>
       <c r="C39">
-        <v>0.826</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="2">
-        <v>46300.39583333334</v>
+        <v>46307.39583333334</v>
       </c>
       <c r="B40">
-        <v>1.365</v>
+        <v>1.146</v>
       </c>
       <c r="C40">
-        <v>0.858</v>
+        <v>4.391</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="2">
-        <v>46300.40625</v>
+        <v>46307.40625</v>
       </c>
       <c r="B41">
-        <v>4.933</v>
+        <v>15.646</v>
       </c>
       <c r="C41">
-        <v>0.585</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="2">
-        <v>46300.41666666666</v>
+        <v>46307.41666666666</v>
       </c>
       <c r="B42">
-        <v>21.638</v>
+        <v>0</v>
       </c>
       <c r="C42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="2">
-        <v>46300.42708333334</v>
-      </c>
-      <c r="B43">
-        <v>14.528</v>
-      </c>
-      <c r="C43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="2">
-        <v>46300.4375</v>
-      </c>
-      <c r="B44">
-        <v>2.661</v>
-      </c>
-      <c r="C44">
-        <v>7.552</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="2">
-        <v>46300.44791666666</v>
-      </c>
-      <c r="B45">
-        <v>0.023</v>
-      </c>
-      <c r="C45">
-        <v>26.068</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="2">
-        <v>46300.45833333334</v>
-      </c>
-      <c r="B46">
-        <v>0</v>
-      </c>
-      <c r="C46">
-        <v>9.917999999999999</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="2">
-        <v>46300.46875</v>
-      </c>
-      <c r="B47">
-        <v>0.595</v>
-      </c>
-      <c r="C47">
-        <v>12.207</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="2">
-        <v>46300.47916666666</v>
-      </c>
-      <c r="B48">
-        <v>0.6</v>
-      </c>
-      <c r="C48">
-        <v>10.039</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="2">
-        <v>46300.48958333334</v>
-      </c>
-      <c r="B49">
-        <v>1.069</v>
-      </c>
-      <c r="C49">
-        <v>2.162</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="2">
-        <v>46300.5</v>
-      </c>
-      <c r="B50">
-        <v>0</v>
-      </c>
-      <c r="C50">
-        <v>2.425</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="2">
-        <v>46300.51041666666</v>
-      </c>
-      <c r="B51">
-        <v>0</v>
-      </c>
-      <c r="C51">
-        <v>17.135</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="2">
-        <v>46300.52083333334</v>
-      </c>
-      <c r="B52">
-        <v>0</v>
-      </c>
-      <c r="C52">
-        <v>3.117</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="2">
-        <v>46300.53125</v>
-      </c>
-      <c r="B53">
-        <v>3</v>
-      </c>
-      <c r="C53">
-        <v>1.124</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="2">
-        <v>46300.54166666666</v>
-      </c>
-      <c r="B54">
-        <v>1.153</v>
-      </c>
-      <c r="C54">
-        <v>1.686</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="2">
-        <v>46300.55208333334</v>
-      </c>
-      <c r="B55">
-        <v>0.162</v>
-      </c>
-      <c r="C55">
-        <v>1.701</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="2">
-        <v>46300.5625</v>
-      </c>
-      <c r="B56">
-        <v>0</v>
-      </c>
-      <c r="C56">
-        <v>9.475</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="2">
-        <v>46300.57291666666</v>
-      </c>
-      <c r="B57">
-        <v>0</v>
-      </c>
-      <c r="C57">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
+++ b/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -400,452 +400,628 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B2">
-        <v>44.359</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>53.054</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2">
-        <v>46307.01041666666</v>
+        <v>46308.01041666666</v>
       </c>
       <c r="B3">
-        <v>37.504</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>55.826</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2">
-        <v>46307.02083333334</v>
+        <v>46308.02083333334</v>
       </c>
       <c r="B4">
-        <v>15.403</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>14.779</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2">
-        <v>46307.03125</v>
+        <v>46308.03125</v>
       </c>
       <c r="B5">
-        <v>0.275</v>
+        <v>1.208</v>
       </c>
       <c r="C5">
-        <v>12.517</v>
+        <v>2.617</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2">
-        <v>46307.04166666666</v>
+        <v>46308.04166666666</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>3.404</v>
       </c>
       <c r="C6">
-        <v>42.629</v>
+        <v>1.102</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2">
-        <v>46307.05208333334</v>
+        <v>46308.05208333334</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>0.859</v>
       </c>
       <c r="C7">
-        <v>32.285</v>
+        <v>0.181</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2">
-        <v>46307.0625</v>
+        <v>46308.0625</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>1.437</v>
       </c>
       <c r="C8">
-        <v>63.343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2">
-        <v>46307.07291666666</v>
+        <v>46308.07291666666</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>4.317</v>
       </c>
       <c r="C9">
-        <v>44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2">
-        <v>46307.08333333334</v>
+        <v>46308.08333333334</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>0.952</v>
       </c>
       <c r="C10">
-        <v>34.317</v>
+        <v>4.865</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2">
-        <v>46307.09375</v>
+        <v>46308.09375</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>0.587</v>
       </c>
       <c r="C11">
-        <v>3.607</v>
+        <v>0.052</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2">
-        <v>46307.10416666666</v>
+        <v>46308.10416666666</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>1.427</v>
       </c>
       <c r="C12">
-        <v>29.434</v>
+        <v>0.903</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2">
-        <v>46307.11458333334</v>
+        <v>46308.11458333334</v>
       </c>
       <c r="B13">
-        <v>0.019</v>
+        <v>1.312</v>
       </c>
       <c r="C13">
-        <v>8.378</v>
+        <v>2.631</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2">
-        <v>46307.125</v>
+        <v>46308.125</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>0.503</v>
       </c>
       <c r="C14">
-        <v>7.337</v>
+        <v>1.779</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2">
-        <v>46307.13541666666</v>
+        <v>46308.13541666666</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>6.852</v>
       </c>
       <c r="C15">
-        <v>1.625</v>
+        <v>0.093</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2">
-        <v>46307.14583333334</v>
+        <v>46308.14583333334</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>0.753</v>
       </c>
       <c r="C16">
-        <v>3.989</v>
+        <v>3.049</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2">
-        <v>46307.15625</v>
+        <v>46308.15625</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>1.929</v>
       </c>
       <c r="C17">
-        <v>22.469</v>
+        <v>1.389</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2">
-        <v>46307.16666666666</v>
+        <v>46308.16666666666</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>0.114</v>
       </c>
       <c r="C18">
-        <v>19.057</v>
+        <v>12.555</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2">
-        <v>46307.17708333334</v>
+        <v>46308.17708333334</v>
       </c>
       <c r="B19">
-        <v>2.563</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>2.735</v>
+        <v>4.895</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2">
-        <v>46307.1875</v>
+        <v>46308.1875</v>
       </c>
       <c r="B20">
-        <v>6.725</v>
+        <v>2.76</v>
       </c>
       <c r="C20">
-        <v>0.053</v>
+        <v>5.816</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2">
-        <v>46307.19791666666</v>
+        <v>46308.19791666666</v>
       </c>
       <c r="B21">
-        <v>5.557</v>
+        <v>5.396</v>
       </c>
       <c r="C21">
-        <v>0.011</v>
+        <v>5.393</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2">
-        <v>46307.20833333334</v>
+        <v>46308.20833333334</v>
       </c>
       <c r="B22">
-        <v>2.568</v>
+        <v>2.585</v>
       </c>
       <c r="C22">
-        <v>12.933</v>
+        <v>1.405</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2">
-        <v>46307.21875</v>
+        <v>46308.21875</v>
       </c>
       <c r="B23">
-        <v>0.004</v>
+        <v>0.146</v>
       </c>
       <c r="C23">
-        <v>12.166</v>
+        <v>1.273</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2">
-        <v>46307.22916666666</v>
+        <v>46308.22916666666</v>
       </c>
       <c r="B24">
-        <v>2.081</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>0.748</v>
+        <v>14.641</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2">
-        <v>46307.23958333334</v>
+        <v>46308.23958333334</v>
       </c>
       <c r="B25">
-        <v>15.296</v>
+        <v>0.848</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>20.428</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2">
-        <v>46307.25</v>
+        <v>46308.25</v>
       </c>
       <c r="B26">
-        <v>11.418</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>17.71</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2">
-        <v>46307.26041666666</v>
+        <v>46308.26041666666</v>
       </c>
       <c r="B27">
-        <v>0.917</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>32.134</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2">
-        <v>46307.27083333334</v>
+        <v>46308.27083333334</v>
       </c>
       <c r="B28">
-        <v>2.033</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>18.93</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2">
-        <v>46307.28125</v>
+        <v>46308.28125</v>
       </c>
       <c r="B29">
-        <v>3.496</v>
+        <v>0</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>21.579</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2">
-        <v>46307.29166666666</v>
+        <v>46308.29166666666</v>
       </c>
       <c r="B30">
-        <v>14.085</v>
+        <v>0</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>41.256</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2">
-        <v>46307.30208333334</v>
+        <v>46308.30208333334</v>
       </c>
       <c r="B31">
-        <v>2.808</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>39.617</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2">
-        <v>46307.3125</v>
+        <v>46308.3125</v>
       </c>
       <c r="B32">
-        <v>0.157</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>0.122</v>
+        <v>33.673</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2">
-        <v>46307.32291666666</v>
+        <v>46308.32291666666</v>
       </c>
       <c r="B33">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <v>9.9</v>
+        <v>56.982</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2">
-        <v>46307.33333333334</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="B34">
         <v>0</v>
       </c>
       <c r="C34">
-        <v>37.099</v>
+        <v>45.613</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2">
-        <v>46307.34375</v>
+        <v>46308.34375</v>
       </c>
       <c r="B35">
         <v>0</v>
       </c>
       <c r="C35">
-        <v>23.986</v>
+        <v>26.625</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2">
-        <v>46307.35416666666</v>
+        <v>46308.35416666666</v>
       </c>
       <c r="B36">
         <v>0</v>
       </c>
       <c r="C36">
-        <v>9.470000000000001</v>
+        <v>45.484</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2">
-        <v>46307.36458333334</v>
+        <v>46308.36458333334</v>
       </c>
       <c r="B37">
         <v>0</v>
       </c>
       <c r="C37">
-        <v>19.004</v>
+        <v>45.228</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2">
-        <v>46307.375</v>
+        <v>46308.375</v>
       </c>
       <c r="B38">
-        <v>0.021</v>
+        <v>0.027</v>
       </c>
       <c r="C38">
-        <v>5.716</v>
+        <v>14.389</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="2">
-        <v>46307.38541666666</v>
+        <v>46308.38541666666</v>
       </c>
       <c r="B39">
-        <v>8.93</v>
+        <v>1.101</v>
       </c>
       <c r="C39">
-        <v>0.037</v>
+        <v>0.602</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="2">
-        <v>46307.39583333334</v>
+        <v>46308.39583333334</v>
       </c>
       <c r="B40">
-        <v>1.146</v>
+        <v>1.704</v>
       </c>
       <c r="C40">
-        <v>4.391</v>
+        <v>0.706</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="2">
-        <v>46307.40625</v>
+        <v>46308.40625</v>
       </c>
       <c r="B41">
-        <v>15.646</v>
+        <v>0.598</v>
       </c>
       <c r="C41">
-        <v>0.012</v>
+        <v>2.306</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="2">
-        <v>46307.41666666666</v>
+        <v>46308.41666666666</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>25.315</v>
       </c>
       <c r="C42">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="2">
+        <v>46308.42708333334</v>
+      </c>
+      <c r="B43">
+        <v>19.956</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="2">
+        <v>46308.4375</v>
+      </c>
+      <c r="B44">
+        <v>6.191</v>
+      </c>
+      <c r="C44">
+        <v>0.6860000000000001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="2">
+        <v>46308.44791666666</v>
+      </c>
+      <c r="B45">
+        <v>0.197</v>
+      </c>
+      <c r="C45">
+        <v>4.82</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="2">
+        <v>46308.45833333334</v>
+      </c>
+      <c r="B46">
+        <v>0.199</v>
+      </c>
+      <c r="C46">
+        <v>4.313</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="2">
+        <v>46308.46875</v>
+      </c>
+      <c r="B47">
+        <v>0</v>
+      </c>
+      <c r="C47">
+        <v>34.445</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="2">
+        <v>46308.47916666666</v>
+      </c>
+      <c r="B48">
+        <v>0</v>
+      </c>
+      <c r="C48">
+        <v>55.886</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="2">
+        <v>46308.48958333334</v>
+      </c>
+      <c r="B49">
+        <v>0</v>
+      </c>
+      <c r="C49">
+        <v>55.345</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="2">
+        <v>46308.5</v>
+      </c>
+      <c r="B50">
+        <v>0</v>
+      </c>
+      <c r="C50">
+        <v>18.127</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="2">
+        <v>46308.51041666666</v>
+      </c>
+      <c r="B51">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="C51">
+        <v>11.316</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="2">
+        <v>46308.52083333334</v>
+      </c>
+      <c r="B52">
+        <v>2.532</v>
+      </c>
+      <c r="C52">
+        <v>1.062</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="2">
+        <v>46308.53125</v>
+      </c>
+      <c r="B53">
+        <v>3.347</v>
+      </c>
+      <c r="C53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="2">
+        <v>46308.54166666666</v>
+      </c>
+      <c r="B54">
+        <v>8.285</v>
+      </c>
+      <c r="C54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" s="2">
+        <v>46308.55208333334</v>
+      </c>
+      <c r="B55">
+        <v>1.978</v>
+      </c>
+      <c r="C55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" s="2">
+        <v>46308.5625</v>
+      </c>
+      <c r="B56">
+        <v>16.049</v>
+      </c>
+      <c r="C56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" s="2">
+        <v>46308.57291666666</v>
+      </c>
+      <c r="B57">
+        <v>40.467</v>
+      </c>
+      <c r="C57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" s="2">
+        <v>46308.58333333334</v>
+      </c>
+      <c r="B58">
+        <v>0</v>
+      </c>
+      <c r="C58">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
+++ b/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C58"/>
+  <dimension ref="A1:C62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -400,461 +400,461 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>12.553</v>
       </c>
       <c r="C2">
-        <v>53.054</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2">
-        <v>46308.01041666666</v>
+        <v>46309.01041666666</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>1.554</v>
       </c>
       <c r="C3">
-        <v>55.826</v>
+        <v>4.069</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2">
-        <v>46308.02083333334</v>
+        <v>46309.02083333334</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>1.981</v>
       </c>
       <c r="C4">
-        <v>14.779</v>
+        <v>0.381</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2">
-        <v>46308.03125</v>
+        <v>46309.03125</v>
       </c>
       <c r="B5">
-        <v>1.208</v>
+        <v>1.39</v>
       </c>
       <c r="C5">
-        <v>2.617</v>
+        <v>0.855</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2">
-        <v>46308.04166666666</v>
+        <v>46309.04166666666</v>
       </c>
       <c r="B6">
-        <v>3.404</v>
+        <v>0.019</v>
       </c>
       <c r="C6">
-        <v>1.102</v>
+        <v>11.325</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2">
-        <v>46308.05208333334</v>
+        <v>46309.05208333334</v>
       </c>
       <c r="B7">
-        <v>0.859</v>
+        <v>5.631</v>
       </c>
       <c r="C7">
-        <v>0.181</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2">
-        <v>46308.0625</v>
+        <v>46309.0625</v>
       </c>
       <c r="B8">
-        <v>1.437</v>
+        <v>1.331</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>1.322</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2">
-        <v>46308.07291666666</v>
+        <v>46309.07291666666</v>
       </c>
       <c r="B9">
-        <v>4.317</v>
+        <v>10.986</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>0.053</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2">
-        <v>46308.08333333334</v>
+        <v>46309.08333333334</v>
       </c>
       <c r="B10">
-        <v>0.952</v>
+        <v>2.38</v>
       </c>
       <c r="C10">
-        <v>4.865</v>
+        <v>0.082</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2">
-        <v>46308.09375</v>
+        <v>46309.09375</v>
       </c>
       <c r="B11">
-        <v>0.587</v>
+        <v>0.822</v>
       </c>
       <c r="C11">
-        <v>0.052</v>
+        <v>3.785</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2">
-        <v>46308.10416666666</v>
+        <v>46309.10416666666</v>
       </c>
       <c r="B12">
-        <v>1.427</v>
+        <v>0.441</v>
       </c>
       <c r="C12">
-        <v>0.903</v>
+        <v>10.767</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2">
-        <v>46308.11458333334</v>
+        <v>46309.11458333334</v>
       </c>
       <c r="B13">
-        <v>1.312</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>2.631</v>
+        <v>17.43</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2">
-        <v>46308.125</v>
+        <v>46309.125</v>
       </c>
       <c r="B14">
-        <v>0.503</v>
+        <v>0.372</v>
       </c>
       <c r="C14">
-        <v>1.779</v>
+        <v>11.506</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2">
-        <v>46308.13541666666</v>
+        <v>46309.13541666666</v>
       </c>
       <c r="B15">
-        <v>6.852</v>
+        <v>0.004</v>
       </c>
       <c r="C15">
-        <v>0.093</v>
+        <v>4.697</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2">
-        <v>46308.14583333334</v>
+        <v>46309.14583333334</v>
       </c>
       <c r="B16">
-        <v>0.753</v>
+        <v>2.916</v>
       </c>
       <c r="C16">
-        <v>3.049</v>
+        <v>0.481</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2">
-        <v>46308.15625</v>
+        <v>46309.15625</v>
       </c>
       <c r="B17">
-        <v>1.929</v>
+        <v>1.013</v>
       </c>
       <c r="C17">
-        <v>1.389</v>
+        <v>5.306</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2">
-        <v>46308.16666666666</v>
+        <v>46309.16666666666</v>
       </c>
       <c r="B18">
-        <v>0.114</v>
+        <v>1.114</v>
       </c>
       <c r="C18">
-        <v>12.555</v>
+        <v>0.801</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2">
-        <v>46308.17708333334</v>
+        <v>46309.17708333334</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>0.278</v>
       </c>
       <c r="C19">
-        <v>4.895</v>
+        <v>0.278</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2">
-        <v>46308.1875</v>
+        <v>46309.1875</v>
       </c>
       <c r="B20">
-        <v>2.76</v>
+        <v>0.832</v>
       </c>
       <c r="C20">
-        <v>5.816</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2">
-        <v>46308.19791666666</v>
+        <v>46309.19791666666</v>
       </c>
       <c r="B21">
-        <v>5.396</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="C21">
-        <v>5.393</v>
+        <v>4.767</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2">
-        <v>46308.20833333334</v>
+        <v>46309.20833333334</v>
       </c>
       <c r="B22">
-        <v>2.585</v>
+        <v>3.875</v>
       </c>
       <c r="C22">
-        <v>1.405</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2">
-        <v>46308.21875</v>
+        <v>46309.21875</v>
       </c>
       <c r="B23">
-        <v>0.146</v>
+        <v>2.555</v>
       </c>
       <c r="C23">
-        <v>1.273</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2">
-        <v>46308.22916666666</v>
+        <v>46309.22916666666</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>1.805</v>
       </c>
       <c r="C24">
-        <v>14.641</v>
+        <v>0.254</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2">
-        <v>46308.23958333334</v>
+        <v>46309.23958333334</v>
       </c>
       <c r="B25">
-        <v>0.848</v>
+        <v>3.565</v>
       </c>
       <c r="C25">
-        <v>20.428</v>
+        <v>0.314</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2">
-        <v>46308.25</v>
+        <v>46309.25</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>4.395</v>
       </c>
       <c r="C26">
-        <v>17.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2">
-        <v>46308.26041666666</v>
+        <v>46309.26041666666</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>2.623</v>
       </c>
       <c r="C27">
-        <v>32.134</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2">
-        <v>46308.27083333334</v>
+        <v>46309.27083333334</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>1.025</v>
       </c>
       <c r="C28">
-        <v>18.93</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2">
-        <v>46308.28125</v>
+        <v>46309.28125</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>5.601</v>
       </c>
       <c r="C29">
-        <v>21.579</v>
+        <v>0.368</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2">
-        <v>46308.29166666666</v>
+        <v>46309.29166666666</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>0.059</v>
       </c>
       <c r="C30">
-        <v>41.256</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2">
-        <v>46308.30208333334</v>
+        <v>46309.30208333334</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="C31">
-        <v>39.617</v>
+        <v>18.607</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2">
-        <v>46308.3125</v>
+        <v>46309.3125</v>
       </c>
       <c r="B32">
         <v>0</v>
       </c>
       <c r="C32">
-        <v>33.673</v>
+        <v>66.886</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2">
-        <v>46308.32291666666</v>
+        <v>46309.32291666666</v>
       </c>
       <c r="B33">
         <v>0</v>
       </c>
       <c r="C33">
-        <v>56.982</v>
+        <v>63.622</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2">
-        <v>46308.33333333334</v>
+        <v>46309.33333333334</v>
       </c>
       <c r="B34">
         <v>0</v>
       </c>
       <c r="C34">
-        <v>45.613</v>
+        <v>86.044</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2">
-        <v>46308.34375</v>
+        <v>46309.34375</v>
       </c>
       <c r="B35">
         <v>0</v>
       </c>
       <c r="C35">
-        <v>26.625</v>
+        <v>61.024</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2">
-        <v>46308.35416666666</v>
+        <v>46309.35416666666</v>
       </c>
       <c r="B36">
         <v>0</v>
       </c>
       <c r="C36">
-        <v>45.484</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2">
-        <v>46308.36458333334</v>
+        <v>46309.36458333334</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="C37">
-        <v>45.228</v>
+        <v>23.465</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2">
-        <v>46308.375</v>
+        <v>46309.375</v>
       </c>
       <c r="B38">
-        <v>0.027</v>
+        <v>0</v>
       </c>
       <c r="C38">
-        <v>14.389</v>
+        <v>39.171</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="2">
-        <v>46308.38541666666</v>
+        <v>46309.38541666666</v>
       </c>
       <c r="B39">
-        <v>1.101</v>
+        <v>8.195</v>
       </c>
       <c r="C39">
-        <v>0.602</v>
+        <v>0.101</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="2">
-        <v>46308.39583333334</v>
+        <v>46309.39583333334</v>
       </c>
       <c r="B40">
-        <v>1.704</v>
+        <v>0.539</v>
       </c>
       <c r="C40">
-        <v>0.706</v>
+        <v>5.051</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="2">
-        <v>46308.40625</v>
+        <v>46309.40625</v>
       </c>
       <c r="B41">
-        <v>0.598</v>
+        <v>0.221</v>
       </c>
       <c r="C41">
-        <v>2.306</v>
+        <v>4.072</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="2">
-        <v>46308.41666666666</v>
+        <v>46309.41666666666</v>
       </c>
       <c r="B42">
-        <v>25.315</v>
+        <v>14.424</v>
       </c>
       <c r="C42">
-        <v>0.002</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="2">
-        <v>46308.42708333334</v>
+        <v>46309.42708333334</v>
       </c>
       <c r="B43">
-        <v>19.956</v>
+        <v>0.831</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -862,166 +862,210 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="2">
-        <v>46308.4375</v>
+        <v>46309.4375</v>
       </c>
       <c r="B44">
-        <v>6.191</v>
+        <v>0.995</v>
       </c>
       <c r="C44">
-        <v>0.6860000000000001</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="2">
-        <v>46308.44791666666</v>
+        <v>46309.44791666666</v>
       </c>
       <c r="B45">
-        <v>0.197</v>
+        <v>0</v>
       </c>
       <c r="C45">
-        <v>4.82</v>
+        <v>9.904</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="2">
-        <v>46308.45833333334</v>
+        <v>46309.45833333334</v>
       </c>
       <c r="B46">
-        <v>0.199</v>
+        <v>0</v>
       </c>
       <c r="C46">
-        <v>4.313</v>
+        <v>13.877</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="2">
-        <v>46308.46875</v>
+        <v>46309.46875</v>
       </c>
       <c r="B47">
         <v>0</v>
       </c>
       <c r="C47">
-        <v>34.445</v>
+        <v>10.195</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="2">
-        <v>46308.47916666666</v>
+        <v>46309.47916666666</v>
       </c>
       <c r="B48">
         <v>0</v>
       </c>
       <c r="C48">
-        <v>55.886</v>
+        <v>23.042</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="2">
-        <v>46308.48958333334</v>
+        <v>46309.48958333334</v>
       </c>
       <c r="B49">
         <v>0</v>
       </c>
       <c r="C49">
-        <v>55.345</v>
+        <v>7.187</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="2">
-        <v>46308.5</v>
+        <v>46309.5</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>0.264</v>
       </c>
       <c r="C50">
-        <v>18.127</v>
+        <v>4.334</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="2">
-        <v>46308.51041666666</v>
+        <v>46309.51041666666</v>
       </c>
       <c r="B51">
-        <v>0.08400000000000001</v>
+        <v>0</v>
       </c>
       <c r="C51">
-        <v>11.316</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="2">
-        <v>46308.52083333334</v>
+        <v>46309.52083333334</v>
       </c>
       <c r="B52">
-        <v>2.532</v>
+        <v>0</v>
       </c>
       <c r="C52">
-        <v>1.062</v>
+        <v>2.188</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="2">
-        <v>46308.53125</v>
+        <v>46309.53125</v>
       </c>
       <c r="B53">
-        <v>3.347</v>
+        <v>0</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>11.27</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="2">
-        <v>46308.54166666666</v>
+        <v>46309.54166666666</v>
       </c>
       <c r="B54">
-        <v>8.285</v>
+        <v>0</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>32.659</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="2">
-        <v>46308.55208333334</v>
+        <v>46309.55208333334</v>
       </c>
       <c r="B55">
-        <v>1.978</v>
+        <v>0.002</v>
       </c>
       <c r="C55">
-        <v>0</v>
+        <v>23.799</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="2">
-        <v>46308.5625</v>
+        <v>46309.5625</v>
       </c>
       <c r="B56">
-        <v>16.049</v>
+        <v>0</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>13.553</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="2">
-        <v>46308.57291666666</v>
+        <v>46309.57291666666</v>
       </c>
       <c r="B57">
-        <v>40.467</v>
+        <v>0</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="2">
-        <v>46308.58333333334</v>
+        <v>46309.58333333334</v>
       </c>
       <c r="B58">
         <v>0</v>
       </c>
       <c r="C58">
+        <v>3.516</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" s="2">
+        <v>46309.59375</v>
+      </c>
+      <c r="B59">
+        <v>0</v>
+      </c>
+      <c r="C59">
+        <v>14.799</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" s="2">
+        <v>46309.60416666666</v>
+      </c>
+      <c r="B60">
+        <v>0</v>
+      </c>
+      <c r="C60">
+        <v>21.33</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" s="2">
+        <v>46309.61458333334</v>
+      </c>
+      <c r="B61">
+        <v>0</v>
+      </c>
+      <c r="C61">
+        <v>24.18</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" s="2">
+        <v>46309.625</v>
+      </c>
+      <c r="B62">
+        <v>0</v>
+      </c>
+      <c r="C62">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
+++ b/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C62"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -400,461 +400,461 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="B2">
-        <v>12.553</v>
+        <v>0.044</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>17.816</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2">
-        <v>46309.01041666666</v>
+        <v>46311.01041666666</v>
       </c>
       <c r="B3">
-        <v>1.554</v>
+        <v>2.784</v>
       </c>
       <c r="C3">
-        <v>4.069</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2">
-        <v>46309.02083333334</v>
+        <v>46311.02083333334</v>
       </c>
       <c r="B4">
-        <v>1.981</v>
+        <v>6.516</v>
       </c>
       <c r="C4">
-        <v>0.381</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2">
-        <v>46309.03125</v>
+        <v>46311.03125</v>
       </c>
       <c r="B5">
-        <v>1.39</v>
+        <v>0.411</v>
       </c>
       <c r="C5">
-        <v>0.855</v>
+        <v>18.52</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2">
-        <v>46309.04166666666</v>
+        <v>46311.04166666666</v>
       </c>
       <c r="B6">
-        <v>0.019</v>
+        <v>0.125</v>
       </c>
       <c r="C6">
-        <v>11.325</v>
+        <v>13.276</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2">
-        <v>46309.05208333334</v>
+        <v>46311.05208333334</v>
       </c>
       <c r="B7">
-        <v>5.631</v>
+        <v>0.001</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>16.86</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2">
-        <v>46309.0625</v>
+        <v>46311.0625</v>
       </c>
       <c r="B8">
-        <v>1.331</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>1.322</v>
+        <v>49.866</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2">
-        <v>46309.07291666666</v>
+        <v>46311.07291666666</v>
       </c>
       <c r="B9">
-        <v>10.986</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>0.053</v>
+        <v>58.08</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2">
-        <v>46309.08333333334</v>
+        <v>46311.08333333334</v>
       </c>
       <c r="B10">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>0.082</v>
+        <v>62.826</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2">
-        <v>46309.09375</v>
+        <v>46311.09375</v>
       </c>
       <c r="B11">
-        <v>0.822</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>3.785</v>
+        <v>33.371</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2">
-        <v>46309.10416666666</v>
+        <v>46311.10416666666</v>
       </c>
       <c r="B12">
-        <v>0.441</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>10.767</v>
+        <v>24.707</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2">
-        <v>46309.11458333334</v>
+        <v>46311.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
       <c r="C13">
-        <v>17.43</v>
+        <v>17.697</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2">
-        <v>46309.125</v>
+        <v>46311.125</v>
       </c>
       <c r="B14">
-        <v>0.372</v>
+        <v>0.751</v>
       </c>
       <c r="C14">
-        <v>11.506</v>
+        <v>3.188</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2">
-        <v>46309.13541666666</v>
+        <v>46311.13541666666</v>
       </c>
       <c r="B15">
-        <v>0.004</v>
+        <v>0.078</v>
       </c>
       <c r="C15">
-        <v>4.697</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2">
-        <v>46309.14583333334</v>
+        <v>46311.14583333334</v>
       </c>
       <c r="B16">
-        <v>2.916</v>
+        <v>0.248</v>
       </c>
       <c r="C16">
-        <v>0.481</v>
+        <v>5.347</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2">
-        <v>46309.15625</v>
+        <v>46311.15625</v>
       </c>
       <c r="B17">
-        <v>1.013</v>
+        <v>0.654</v>
       </c>
       <c r="C17">
-        <v>5.306</v>
+        <v>1.457</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2">
-        <v>46309.16666666666</v>
+        <v>46311.16666666666</v>
       </c>
       <c r="B18">
-        <v>1.114</v>
+        <v>0</v>
       </c>
       <c r="C18">
-        <v>0.801</v>
+        <v>21.622</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2">
-        <v>46309.17708333334</v>
+        <v>46311.17708333334</v>
       </c>
       <c r="B19">
-        <v>0.278</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>0.278</v>
+        <v>12.874</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2">
-        <v>46309.1875</v>
+        <v>46311.1875</v>
       </c>
       <c r="B20">
-        <v>0.832</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>17.396</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2">
-        <v>46309.19791666666</v>
+        <v>46311.19791666666</v>
       </c>
       <c r="B21">
-        <v>0.5590000000000001</v>
+        <v>0</v>
       </c>
       <c r="C21">
-        <v>4.767</v>
+        <v>22.629</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2">
-        <v>46309.20833333334</v>
+        <v>46311.20833333334</v>
       </c>
       <c r="B22">
-        <v>3.875</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>14.436</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2">
-        <v>46309.21875</v>
+        <v>46311.21875</v>
       </c>
       <c r="B23">
-        <v>2.555</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>16.153</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2">
-        <v>46309.22916666666</v>
+        <v>46311.22916666666</v>
       </c>
       <c r="B24">
-        <v>1.805</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>0.254</v>
+        <v>26.873</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2">
-        <v>46309.23958333334</v>
+        <v>46311.23958333334</v>
       </c>
       <c r="B25">
-        <v>3.565</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>0.314</v>
+        <v>26.627</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2">
-        <v>46309.25</v>
+        <v>46311.25</v>
       </c>
       <c r="B26">
-        <v>4.395</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>45.761</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2">
-        <v>46309.26041666666</v>
+        <v>46311.26041666666</v>
       </c>
       <c r="B27">
-        <v>2.623</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>44.978</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2">
-        <v>46309.27083333334</v>
+        <v>46311.27083333334</v>
       </c>
       <c r="B28">
-        <v>1.025</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>0.005</v>
+        <v>46.714</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2">
-        <v>46309.28125</v>
+        <v>46311.28125</v>
       </c>
       <c r="B29">
-        <v>5.601</v>
+        <v>0</v>
       </c>
       <c r="C29">
-        <v>0.368</v>
+        <v>36.707</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2">
-        <v>46309.29166666666</v>
+        <v>46311.29166666666</v>
       </c>
       <c r="B30">
-        <v>0.059</v>
+        <v>0</v>
       </c>
       <c r="C30">
-        <v>3.71</v>
+        <v>17.267</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2">
-        <v>46309.30208333334</v>
+        <v>46311.30208333334</v>
       </c>
       <c r="B31">
-        <v>0.005</v>
+        <v>0.052</v>
       </c>
       <c r="C31">
-        <v>18.607</v>
+        <v>9.388999999999999</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2">
-        <v>46309.3125</v>
+        <v>46311.3125</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>0.131</v>
       </c>
       <c r="C32">
-        <v>66.886</v>
+        <v>13.847</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2">
-        <v>46309.32291666666</v>
+        <v>46311.32291666666</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>0.229</v>
       </c>
       <c r="C33">
-        <v>63.622</v>
+        <v>11.05</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2">
-        <v>46309.33333333334</v>
+        <v>46311.33333333334</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>0.837</v>
       </c>
       <c r="C34">
-        <v>86.044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2">
-        <v>46309.34375</v>
+        <v>46311.34375</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>0.117</v>
       </c>
       <c r="C35">
-        <v>61.024</v>
+        <v>3.081</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2">
-        <v>46309.35416666666</v>
+        <v>46311.35416666666</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>3.204</v>
       </c>
       <c r="C36">
-        <v>40.4</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2">
-        <v>46309.36458333334</v>
+        <v>46311.36458333334</v>
       </c>
       <c r="B37">
-        <v>0.002</v>
+        <v>0.038</v>
       </c>
       <c r="C37">
-        <v>23.465</v>
+        <v>33.427</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2">
-        <v>46309.375</v>
+        <v>46311.375</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>0.108</v>
       </c>
       <c r="C38">
-        <v>39.171</v>
+        <v>20.094</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="2">
-        <v>46309.38541666666</v>
+        <v>46311.38541666666</v>
       </c>
       <c r="B39">
-        <v>8.195</v>
+        <v>0</v>
       </c>
       <c r="C39">
-        <v>0.101</v>
+        <v>41.921</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="2">
-        <v>46309.39583333334</v>
+        <v>46311.39583333334</v>
       </c>
       <c r="B40">
-        <v>0.539</v>
+        <v>0</v>
       </c>
       <c r="C40">
-        <v>5.051</v>
+        <v>52.461</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="2">
-        <v>46309.40625</v>
+        <v>46311.40625</v>
       </c>
       <c r="B41">
-        <v>0.221</v>
+        <v>0.143</v>
       </c>
       <c r="C41">
-        <v>4.072</v>
+        <v>6.151</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="2">
-        <v>46309.41666666666</v>
+        <v>46311.41666666666</v>
       </c>
       <c r="B42">
-        <v>14.424</v>
+        <v>39.137</v>
       </c>
       <c r="C42">
-        <v>0.036</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="2">
-        <v>46309.42708333334</v>
+        <v>46311.42708333334</v>
       </c>
       <c r="B43">
-        <v>0.831</v>
+        <v>0</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -862,210 +862,122 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="2">
-        <v>46309.4375</v>
+        <v>46311.4375</v>
       </c>
       <c r="B44">
-        <v>0.995</v>
+        <v>1.72</v>
       </c>
       <c r="C44">
-        <v>0.27</v>
+        <v>4.263</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="2">
-        <v>46309.44791666666</v>
+        <v>46311.44791666666</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>14.344</v>
       </c>
       <c r="C45">
-        <v>9.904</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="2">
-        <v>46309.45833333334</v>
+        <v>46311.45833333334</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>15.92</v>
       </c>
       <c r="C46">
-        <v>13.877</v>
+        <v>0.413</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="2">
-        <v>46309.46875</v>
+        <v>46311.46875</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>2.228</v>
       </c>
       <c r="C47">
-        <v>10.195</v>
+        <v>0.911</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="2">
-        <v>46309.47916666666</v>
+        <v>46311.47916666666</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>6.716</v>
       </c>
       <c r="C48">
-        <v>23.042</v>
+        <v>1.776</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="2">
-        <v>46309.48958333334</v>
+        <v>46311.48958333334</v>
       </c>
       <c r="B49">
         <v>0</v>
       </c>
       <c r="C49">
-        <v>7.187</v>
+        <v>20.667</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="2">
-        <v>46309.5</v>
+        <v>46311.5</v>
       </c>
       <c r="B50">
-        <v>0.264</v>
+        <v>0</v>
       </c>
       <c r="C50">
-        <v>4.334</v>
+        <v>44.351</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="2">
-        <v>46309.51041666666</v>
+        <v>46311.51041666666</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>0.134</v>
       </c>
       <c r="C51">
-        <v>0.025</v>
+        <v>27.06</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="2">
-        <v>46309.52083333334</v>
+        <v>46311.52083333334</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="C52">
-        <v>2.188</v>
+        <v>4.003</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="2">
-        <v>46309.53125</v>
+        <v>46311.53125</v>
       </c>
       <c r="B53">
-        <v>0</v>
+        <v>1.187</v>
       </c>
       <c r="C53">
-        <v>11.27</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="2">
-        <v>46309.54166666666</v>
+        <v>46311.54166666666</v>
       </c>
       <c r="B54">
         <v>0</v>
       </c>
       <c r="C54">
-        <v>32.659</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="2">
-        <v>46309.55208333334</v>
-      </c>
-      <c r="B55">
-        <v>0.002</v>
-      </c>
-      <c r="C55">
-        <v>23.799</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="2">
-        <v>46309.5625</v>
-      </c>
-      <c r="B56">
-        <v>0</v>
-      </c>
-      <c r="C56">
-        <v>13.553</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="2">
-        <v>46309.57291666666</v>
-      </c>
-      <c r="B57">
-        <v>0</v>
-      </c>
-      <c r="C57">
-        <v>2.46</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3">
-      <c r="A58" s="2">
-        <v>46309.58333333334</v>
-      </c>
-      <c r="B58">
-        <v>0</v>
-      </c>
-      <c r="C58">
-        <v>3.516</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="2">
-        <v>46309.59375</v>
-      </c>
-      <c r="B59">
-        <v>0</v>
-      </c>
-      <c r="C59">
-        <v>14.799</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="2">
-        <v>46309.60416666666</v>
-      </c>
-      <c r="B60">
-        <v>0</v>
-      </c>
-      <c r="C60">
-        <v>21.33</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3">
-      <c r="A61" s="2">
-        <v>46309.61458333334</v>
-      </c>
-      <c r="B61">
-        <v>0</v>
-      </c>
-      <c r="C61">
-        <v>24.18</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3">
-      <c r="A62" s="2">
-        <v>46309.625</v>
-      </c>
-      <c r="B62">
-        <v>0</v>
-      </c>
-      <c r="C62">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
+++ b/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -400,362 +400,362 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2">
-        <v>46311</v>
+        <v>46316</v>
       </c>
       <c r="B2">
-        <v>0.044</v>
+        <v>1.604</v>
       </c>
       <c r="C2">
-        <v>17.816</v>
+        <v>7.861</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2">
-        <v>46311.01041666666</v>
+        <v>46316.01041666666</v>
       </c>
       <c r="B3">
-        <v>2.784</v>
+        <v>0.129</v>
       </c>
       <c r="C3">
-        <v>0.66</v>
+        <v>6.127</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2">
-        <v>46311.02083333334</v>
+        <v>46316.02083333334</v>
       </c>
       <c r="B4">
-        <v>6.516</v>
+        <v>4.337</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>0.126</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2">
-        <v>46311.03125</v>
+        <v>46316.03125</v>
       </c>
       <c r="B5">
-        <v>0.411</v>
+        <v>8.055999999999999</v>
       </c>
       <c r="C5">
-        <v>18.52</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2">
-        <v>46311.04166666666</v>
+        <v>46316.04166666666</v>
       </c>
       <c r="B6">
-        <v>0.125</v>
+        <v>0.478</v>
       </c>
       <c r="C6">
-        <v>13.276</v>
+        <v>6.195</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2">
-        <v>46311.05208333334</v>
+        <v>46316.05208333334</v>
       </c>
       <c r="B7">
-        <v>0.001</v>
+        <v>13.745</v>
       </c>
       <c r="C7">
-        <v>16.86</v>
+        <v>0.378</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2">
-        <v>46311.0625</v>
+        <v>46316.0625</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="C8">
-        <v>49.866</v>
+        <v>2.089</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2">
-        <v>46311.07291666666</v>
+        <v>46316.07291666666</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>5.253</v>
       </c>
       <c r="C9">
-        <v>58.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2">
-        <v>46311.08333333334</v>
+        <v>46316.08333333334</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>1.719</v>
       </c>
       <c r="C10">
-        <v>62.826</v>
+        <v>0.469</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2">
-        <v>46311.09375</v>
+        <v>46316.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
       <c r="C11">
-        <v>33.371</v>
+        <v>18.139</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2">
-        <v>46311.10416666666</v>
+        <v>46316.10416666666</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>0.238</v>
       </c>
       <c r="C12">
-        <v>24.707</v>
+        <v>4.198</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2">
-        <v>46311.11458333334</v>
+        <v>46316.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
       <c r="C13">
-        <v>17.697</v>
+        <v>16.42</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2">
-        <v>46311.125</v>
+        <v>46316.125</v>
       </c>
       <c r="B14">
-        <v>0.751</v>
+        <v>0.003</v>
       </c>
       <c r="C14">
-        <v>3.188</v>
+        <v>10.458</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2">
-        <v>46311.13541666666</v>
+        <v>46316.13541666666</v>
       </c>
       <c r="B15">
-        <v>0.078</v>
+        <v>1.892</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2">
-        <v>46311.14583333334</v>
+        <v>46316.14583333334</v>
       </c>
       <c r="B16">
-        <v>0.248</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="C16">
-        <v>5.347</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2">
-        <v>46311.15625</v>
+        <v>46316.15625</v>
       </c>
       <c r="B17">
-        <v>0.654</v>
+        <v>0</v>
       </c>
       <c r="C17">
-        <v>1.457</v>
+        <v>30.116</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2">
-        <v>46311.16666666666</v>
+        <v>46316.16666666666</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>1.537</v>
       </c>
       <c r="C18">
-        <v>21.622</v>
+        <v>3.761</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2">
-        <v>46311.17708333334</v>
+        <v>46316.17708333334</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="C19">
-        <v>12.874</v>
+        <v>44.873</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2">
-        <v>46311.1875</v>
+        <v>46316.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
       </c>
       <c r="C20">
-        <v>17.396</v>
+        <v>38.957</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2">
-        <v>46311.19791666666</v>
+        <v>46316.19791666666</v>
       </c>
       <c r="B21">
         <v>0</v>
       </c>
       <c r="C21">
-        <v>22.629</v>
+        <v>64.34999999999999</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2">
-        <v>46311.20833333334</v>
+        <v>46316.20833333334</v>
       </c>
       <c r="B22">
         <v>0</v>
       </c>
       <c r="C22">
-        <v>14.436</v>
+        <v>52.155</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2">
-        <v>46311.21875</v>
+        <v>46316.21875</v>
       </c>
       <c r="B23">
         <v>0</v>
       </c>
       <c r="C23">
-        <v>16.153</v>
+        <v>45.04</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2">
-        <v>46311.22916666666</v>
+        <v>46316.22916666666</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>0.329</v>
       </c>
       <c r="C24">
-        <v>26.873</v>
+        <v>1.182</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2">
-        <v>46311.23958333334</v>
+        <v>46316.23958333334</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>1.785</v>
       </c>
       <c r="C25">
-        <v>26.627</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2">
-        <v>46311.25</v>
+        <v>46316.25</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="C26">
-        <v>45.761</v>
+        <v>5.186</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2">
-        <v>46311.26041666666</v>
+        <v>46316.26041666666</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>0.151</v>
       </c>
       <c r="C27">
-        <v>44.978</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2">
-        <v>46311.27083333334</v>
+        <v>46316.27083333334</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>0.338</v>
       </c>
       <c r="C28">
-        <v>46.714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2">
-        <v>46311.28125</v>
+        <v>46316.28125</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>0.702</v>
       </c>
       <c r="C29">
-        <v>36.707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2">
-        <v>46311.29166666666</v>
+        <v>46316.29166666666</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="C30">
-        <v>17.267</v>
+        <v>4.532</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2">
-        <v>46311.30208333334</v>
+        <v>46316.30208333334</v>
       </c>
       <c r="B31">
-        <v>0.052</v>
+        <v>0.553</v>
       </c>
       <c r="C31">
-        <v>9.388999999999999</v>
+        <v>1.924</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2">
-        <v>46311.3125</v>
+        <v>46316.3125</v>
       </c>
       <c r="B32">
-        <v>0.131</v>
+        <v>0.418</v>
       </c>
       <c r="C32">
-        <v>13.847</v>
+        <v>7.918</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2">
-        <v>46311.32291666666</v>
+        <v>46316.32291666666</v>
       </c>
       <c r="B33">
-        <v>0.229</v>
+        <v>8.326000000000001</v>
       </c>
       <c r="C33">
-        <v>11.05</v>
+        <v>1.027</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2">
-        <v>46311.33333333334</v>
+        <v>46316.33333333334</v>
       </c>
       <c r="B34">
-        <v>0.837</v>
+        <v>19.843</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -763,221 +763,45 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2">
-        <v>46311.34375</v>
+        <v>46316.34375</v>
       </c>
       <c r="B35">
-        <v>0.117</v>
+        <v>15.821</v>
       </c>
       <c r="C35">
-        <v>3.081</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2">
-        <v>46311.35416666666</v>
+        <v>46316.35416666666</v>
       </c>
       <c r="B36">
-        <v>3.204</v>
+        <v>15.156</v>
       </c>
       <c r="C36">
-        <v>1.89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2">
-        <v>46311.36458333334</v>
+        <v>46316.36458333334</v>
       </c>
       <c r="B37">
-        <v>0.038</v>
+        <v>9.407</v>
       </c>
       <c r="C37">
-        <v>33.427</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2">
-        <v>46311.375</v>
+        <v>46316.375</v>
       </c>
       <c r="B38">
-        <v>0.108</v>
+        <v>0</v>
       </c>
       <c r="C38">
-        <v>20.094</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="2">
-        <v>46311.38541666666</v>
-      </c>
-      <c r="B39">
-        <v>0</v>
-      </c>
-      <c r="C39">
-        <v>41.921</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="2">
-        <v>46311.39583333334</v>
-      </c>
-      <c r="B40">
-        <v>0</v>
-      </c>
-      <c r="C40">
-        <v>52.461</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="2">
-        <v>46311.40625</v>
-      </c>
-      <c r="B41">
-        <v>0.143</v>
-      </c>
-      <c r="C41">
-        <v>6.151</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="2">
-        <v>46311.41666666666</v>
-      </c>
-      <c r="B42">
-        <v>39.137</v>
-      </c>
-      <c r="C42">
-        <v>0.016</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="2">
-        <v>46311.42708333334</v>
-      </c>
-      <c r="B43">
-        <v>0</v>
-      </c>
-      <c r="C43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="2">
-        <v>46311.4375</v>
-      </c>
-      <c r="B44">
-        <v>1.72</v>
-      </c>
-      <c r="C44">
-        <v>4.263</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="2">
-        <v>46311.44791666666</v>
-      </c>
-      <c r="B45">
-        <v>14.344</v>
-      </c>
-      <c r="C45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="2">
-        <v>46311.45833333334</v>
-      </c>
-      <c r="B46">
-        <v>15.92</v>
-      </c>
-      <c r="C46">
-        <v>0.413</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="2">
-        <v>46311.46875</v>
-      </c>
-      <c r="B47">
-        <v>2.228</v>
-      </c>
-      <c r="C47">
-        <v>0.911</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="2">
-        <v>46311.47916666666</v>
-      </c>
-      <c r="B48">
-        <v>6.716</v>
-      </c>
-      <c r="C48">
-        <v>1.776</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="2">
-        <v>46311.48958333334</v>
-      </c>
-      <c r="B49">
-        <v>0</v>
-      </c>
-      <c r="C49">
-        <v>20.667</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="2">
-        <v>46311.5</v>
-      </c>
-      <c r="B50">
-        <v>0</v>
-      </c>
-      <c r="C50">
-        <v>44.351</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="2">
-        <v>46311.51041666666</v>
-      </c>
-      <c r="B51">
-        <v>0.134</v>
-      </c>
-      <c r="C51">
-        <v>27.06</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="2">
-        <v>46311.52083333334</v>
-      </c>
-      <c r="B52">
-        <v>0.79</v>
-      </c>
-      <c r="C52">
-        <v>4.003</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="2">
-        <v>46311.53125</v>
-      </c>
-      <c r="B53">
-        <v>1.187</v>
-      </c>
-      <c r="C53">
-        <v>0.025</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="2">
-        <v>46311.54166666666</v>
-      </c>
-      <c r="B54">
-        <v>0</v>
-      </c>
-      <c r="C54">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
+++ b/data_fetching/Entsoe/IGCC_Netting_Flows.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -400,87 +400,87 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2">
-        <v>46316</v>
+        <v>46320.04166666666</v>
       </c>
       <c r="B2">
-        <v>1.604</v>
+        <v>3.051</v>
       </c>
       <c r="C2">
-        <v>7.861</v>
+        <v>0.457</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2">
-        <v>46316.01041666666</v>
+        <v>46320.05208333334</v>
       </c>
       <c r="B3">
-        <v>0.129</v>
+        <v>16.92</v>
       </c>
       <c r="C3">
-        <v>6.127</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2">
-        <v>46316.02083333334</v>
+        <v>46320.0625</v>
       </c>
       <c r="B4">
-        <v>4.337</v>
+        <v>27.132</v>
       </c>
       <c r="C4">
-        <v>0.126</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2">
-        <v>46316.03125</v>
+        <v>46320.08333333334</v>
       </c>
       <c r="B5">
-        <v>8.055999999999999</v>
+        <v>11.318</v>
       </c>
       <c r="C5">
-        <v>0.014</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2">
-        <v>46316.04166666666</v>
+        <v>46320.09375</v>
       </c>
       <c r="B6">
-        <v>0.478</v>
+        <v>8.125999999999999</v>
       </c>
       <c r="C6">
-        <v>6.195</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2">
-        <v>46316.05208333334</v>
+        <v>46320.10416666666</v>
       </c>
       <c r="B7">
-        <v>13.745</v>
+        <v>5.082</v>
       </c>
       <c r="C7">
-        <v>0.378</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2">
-        <v>46316.0625</v>
+        <v>46320.11458333334</v>
       </c>
       <c r="B8">
-        <v>2.24</v>
+        <v>7.882</v>
       </c>
       <c r="C8">
-        <v>2.089</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2">
-        <v>46316.07291666666</v>
+        <v>46320.125</v>
       </c>
       <c r="B9">
-        <v>5.253</v>
+        <v>5.823</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -488,320 +488,210 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2">
-        <v>46316.08333333334</v>
+        <v>46320.13541666666</v>
       </c>
       <c r="B10">
-        <v>1.719</v>
+        <v>0.051</v>
       </c>
       <c r="C10">
-        <v>0.469</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2">
-        <v>46316.09375</v>
+        <v>46320.14583333334</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
       <c r="C11">
-        <v>18.139</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2">
-        <v>46316.10416666666</v>
+        <v>46320.15625</v>
       </c>
       <c r="B12">
-        <v>0.238</v>
+        <v>3.133</v>
       </c>
       <c r="C12">
-        <v>4.198</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2">
-        <v>46316.11458333334</v>
+        <v>46320.16666666666</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>0.981</v>
       </c>
       <c r="C13">
-        <v>16.42</v>
+        <v>0.124</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2">
-        <v>46316.125</v>
+        <v>46320.17708333334</v>
       </c>
       <c r="B14">
-        <v>0.003</v>
+        <v>3.022</v>
       </c>
       <c r="C14">
-        <v>10.458</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2">
-        <v>46316.13541666666</v>
+        <v>46320.1875</v>
       </c>
       <c r="B15">
-        <v>1.892</v>
+        <v>9.894</v>
       </c>
       <c r="C15">
-        <v>0.024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2">
-        <v>46316.14583333334</v>
+        <v>46320.19791666666</v>
       </c>
       <c r="B16">
-        <v>0.6840000000000001</v>
+        <v>3.848</v>
       </c>
       <c r="C16">
-        <v>7.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2">
-        <v>46316.15625</v>
+        <v>46320.20833333334</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>4.039</v>
       </c>
       <c r="C17">
-        <v>30.116</v>
+        <v>1.226</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2">
-        <v>46316.16666666666</v>
+        <v>46320.21875</v>
       </c>
       <c r="B18">
-        <v>1.537</v>
+        <v>5.904</v>
       </c>
       <c r="C18">
-        <v>3.761</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2">
-        <v>46316.17708333334</v>
+        <v>46320.22916666666</v>
       </c>
       <c r="B19">
-        <v>0.006</v>
+        <v>4.821</v>
       </c>
       <c r="C19">
-        <v>44.873</v>
+        <v>0.129</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2">
-        <v>46316.1875</v>
+        <v>46320.23958333334</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>0.081</v>
       </c>
       <c r="C20">
-        <v>38.957</v>
+        <v>3.607</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2">
-        <v>46316.19791666666</v>
+        <v>46320.25</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>0.313</v>
       </c>
       <c r="C21">
-        <v>64.34999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2">
-        <v>46316.20833333334</v>
+        <v>46320.26041666666</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>13.787</v>
       </c>
       <c r="C22">
-        <v>52.155</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2">
-        <v>46316.21875</v>
+        <v>46320.27083333334</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>2.556</v>
       </c>
       <c r="C23">
-        <v>45.04</v>
+        <v>3.688</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2">
-        <v>46316.22916666666</v>
+        <v>46320.28125</v>
       </c>
       <c r="B24">
-        <v>0.329</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>1.182</v>
+        <v>39.885</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2">
-        <v>46316.23958333334</v>
+        <v>46320.32291666666</v>
       </c>
       <c r="B25">
-        <v>1.785</v>
+        <v>0.013</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>9.962999999999999</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2">
-        <v>46316.25</v>
+        <v>46320.33333333334</v>
       </c>
       <c r="B26">
-        <v>0.06900000000000001</v>
+        <v>0.199</v>
       </c>
       <c r="C26">
-        <v>5.186</v>
+        <v>11.861</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2">
-        <v>46316.26041666666</v>
+        <v>46320.34375</v>
       </c>
       <c r="B27">
-        <v>0.151</v>
+        <v>4.414</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>0.178</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2">
-        <v>46316.27083333334</v>
+        <v>46320.36458333334</v>
       </c>
       <c r="B28">
-        <v>0.338</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="2">
-        <v>46316.28125</v>
-      </c>
-      <c r="B29">
-        <v>0.702</v>
-      </c>
-      <c r="C29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="2">
-        <v>46316.29166666666</v>
-      </c>
-      <c r="B30">
-        <v>0.6919999999999999</v>
-      </c>
-      <c r="C30">
-        <v>4.532</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="2">
-        <v>46316.30208333334</v>
-      </c>
-      <c r="B31">
-        <v>0.553</v>
-      </c>
-      <c r="C31">
-        <v>1.924</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="2">
-        <v>46316.3125</v>
-      </c>
-      <c r="B32">
-        <v>0.418</v>
-      </c>
-      <c r="C32">
-        <v>7.918</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="2">
-        <v>46316.32291666666</v>
-      </c>
-      <c r="B33">
-        <v>8.326000000000001</v>
-      </c>
-      <c r="C33">
-        <v>1.027</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="2">
-        <v>46316.33333333334</v>
-      </c>
-      <c r="B34">
-        <v>19.843</v>
-      </c>
-      <c r="C34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="2">
-        <v>46316.34375</v>
-      </c>
-      <c r="B35">
-        <v>15.821</v>
-      </c>
-      <c r="C35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="2">
-        <v>46316.35416666666</v>
-      </c>
-      <c r="B36">
-        <v>15.156</v>
-      </c>
-      <c r="C36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="2">
-        <v>46316.36458333334</v>
-      </c>
-      <c r="B37">
-        <v>9.407</v>
-      </c>
-      <c r="C37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="2">
-        <v>46316.375</v>
-      </c>
-      <c r="B38">
-        <v>0</v>
-      </c>
-      <c r="C38">
         <v>0</v>
       </c>
     </row>
